--- a/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas 06.10.2025 a 12.10.2025.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas 06.10.2025 a 12.10.2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29401"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29404"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms.sharepoint.com/teams/BR0010-4356589/Shared Documents/BACK-OFFICE SME/Santander/2025/Relatório de Recusas/05. Maio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3BA880BE-01E2-429C-8810-599C7F1E5D50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9F0B08FA-2AEC-481E-9269-AC6335524428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="06.10" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="98">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -239,6 +239,122 @@
   </si>
   <si>
     <t xml:space="preserve">GUILHERME RAMOS MACHADO                      </t>
+  </si>
+  <si>
+    <t>LIMBO</t>
+  </si>
+  <si>
+    <t>LUCIA DOS SANTOS SILVA LTDA ME CNPJ 29919319000105</t>
+  </si>
+  <si>
+    <t>Duplicidade;</t>
+  </si>
+  <si>
+    <t>Localizamos a apólice 5177202551310273256 (ativa) VC 3449920067 em duplicidade com a VC 3450094362, recepcionada via limbo com cobertura para o mesmo risco</t>
+  </si>
+  <si>
+    <t>GEOVANA SUZART SIMOES FERREIRA CPF 51419289500</t>
+  </si>
+  <si>
+    <t>a pedido segurado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JACI MARCONDES                               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEDRO CUSTODIO SANTANA                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">F DA SILVA LEANDRO ME                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE MOREIRA DE SOUSA NETO                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMERCIAL FERREIRA LINCON LTDA EPP           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JONNATHAN CARLOS DE SOUSA VINCIGUERRA        </t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 06.10.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMILTON APARECIDO CONSOLO                    </t>
+  </si>
+  <si>
+    <t>FRUSTRADA: CLIENTE NÃO CORRIGIU A FOTO INCORRETA - PRAZO EXPIRADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZPR INDUSTRIA TEXTIL LTDA ME                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AURENICE MARIA DE AGOSTINHO PRETEL           </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que não
+há possibilidade efetuar a transferência de bônus para o(a) senhor
+(a) AURENICE MARIA DE AGOSTINHO PRETEL, pois este não consta como
+condutor na apólice anterior.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE FERNANDES                               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FABIOLA NERES ALVES DA MOTA                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDERSON LUIS GARCIA                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALEX GRACIEL CARDOSO LOPES                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Favor enviar cópia do endosso de cancelamento da apólice 2025/202
+6 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANOEL GOMES DE MOURA                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAULO HENRIQUE MATOS DA COSTA                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JHANNETH NILDA PEREZ BATALLANOS              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUPERMERCADO LAURA LTDA ME                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JULIANA LUZARDO ALVES                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEDRO HENRIQUE DE ASSIS                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANDRA REGINA DA SILVA ARAUJO                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATHEUS GABRIEL INACIO                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARTUR DIAS LOPES                             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FELIPE SCHMITT LUSTOSA                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">OSWALDO COLMANETTE JUNIOR                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARY FERREIRA COELHO JUNIOR                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EZEQUIAS MACHADO DA SILVA                    </t>
+  </si>
+  <si>
+    <t>Favor enviar cópia completa da apólice referente 2024/2025 (Não
+será aceito a CI, uma vez em que a CBE não retorna os dados)</t>
   </si>
 </sst>
 </file>
@@ -297,7 +413,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -503,12 +619,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -619,16 +746,12 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -638,15 +761,27 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1034,22 +1169,22 @@
       <c r="C2" s="27">
         <v>45936</v>
       </c>
-      <c r="D2" s="46">
+      <c r="D2" s="24">
         <v>134596935</v>
       </c>
-      <c r="E2" s="50">
+      <c r="E2" s="48">
         <v>3450088180</v>
       </c>
-      <c r="F2" s="49" t="s">
+      <c r="F2" s="12" t="s">
         <v>10</v>
       </c>
       <c r="G2" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="55" t="s">
+      <c r="H2" s="52" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="54">
+      <c r="I2" s="51">
         <v>45929</v>
       </c>
     </row>
@@ -1063,22 +1198,22 @@
       <c r="C3" s="27">
         <v>45936</v>
       </c>
-      <c r="D3" s="46">
+      <c r="D3" s="24">
         <v>134652343</v>
       </c>
-      <c r="E3" s="51">
+      <c r="E3" s="49">
         <v>3450091667</v>
       </c>
-      <c r="F3" s="49" t="s">
+      <c r="F3" s="12" t="s">
         <v>13</v>
       </c>
       <c r="G3" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="56" t="s">
+      <c r="H3" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="54">
+      <c r="I3" s="51">
         <v>45926</v>
       </c>
     </row>
@@ -1092,22 +1227,22 @@
       <c r="C4" s="27">
         <v>45936</v>
       </c>
-      <c r="D4" s="46">
+      <c r="D4" s="24">
         <v>134658870</v>
       </c>
-      <c r="E4" s="51">
+      <c r="E4" s="49">
         <v>3450092130</v>
       </c>
-      <c r="F4" s="49" t="s">
+      <c r="F4" s="12" t="s">
         <v>16</v>
       </c>
       <c r="G4" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="56" t="s">
+      <c r="H4" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="54">
+      <c r="I4" s="51">
         <v>45926</v>
       </c>
     </row>
@@ -1121,22 +1256,22 @@
       <c r="C5" s="27">
         <v>45936</v>
       </c>
-      <c r="D5" s="46">
+      <c r="D5" s="24">
         <v>134667095</v>
       </c>
-      <c r="E5" s="51">
+      <c r="E5" s="49">
         <v>3450092712</v>
       </c>
-      <c r="F5" s="49" t="s">
+      <c r="F5" s="12" t="s">
         <v>19</v>
       </c>
       <c r="G5" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="56" t="s">
+      <c r="H5" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="I5" s="54">
+      <c r="I5" s="51">
         <v>45926</v>
       </c>
     </row>
@@ -1150,22 +1285,22 @@
       <c r="C6" s="27">
         <v>45936</v>
       </c>
-      <c r="D6" s="46">
+      <c r="D6" s="24">
         <v>134671678</v>
       </c>
-      <c r="E6" s="51">
+      <c r="E6" s="49">
         <v>3450087498</v>
       </c>
-      <c r="F6" s="49" t="s">
+      <c r="F6" s="12" t="s">
         <v>21</v>
       </c>
       <c r="G6" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="57" t="s">
+      <c r="H6" s="53" t="s">
         <v>18</v>
       </c>
-      <c r="I6" s="54">
+      <c r="I6" s="51">
         <v>45923</v>
       </c>
     </row>
@@ -1179,22 +1314,22 @@
       <c r="C7" s="27">
         <v>45936</v>
       </c>
-      <c r="D7" s="46">
+      <c r="D7" s="24">
         <v>134665477</v>
       </c>
-      <c r="E7" s="51">
+      <c r="E7" s="49">
         <v>3450092547</v>
       </c>
-      <c r="F7" s="49" t="s">
+      <c r="F7" s="12" t="s">
         <v>22</v>
       </c>
       <c r="G7" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="H7" s="58" t="s">
+      <c r="H7" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="I7" s="54">
+      <c r="I7" s="51">
         <v>45926</v>
       </c>
     </row>
@@ -1208,22 +1343,22 @@
       <c r="C8" s="27">
         <v>45936</v>
       </c>
-      <c r="D8" s="46">
+      <c r="D8" s="24">
         <v>134652012</v>
       </c>
-      <c r="E8" s="51">
+      <c r="E8" s="49">
         <v>3450091601</v>
       </c>
-      <c r="F8" s="49" t="s">
+      <c r="F8" s="12" t="s">
         <v>23</v>
       </c>
       <c r="G8" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="H8" s="58" t="s">
+      <c r="H8" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="I8" s="54">
+      <c r="I8" s="51">
         <v>45926</v>
       </c>
     </row>
@@ -1237,22 +1372,22 @@
       <c r="C9" s="27">
         <v>45936</v>
       </c>
-      <c r="D9" s="46">
+      <c r="D9" s="24">
         <v>134656283</v>
       </c>
-      <c r="E9" s="51">
+      <c r="E9" s="49">
         <v>3450090875</v>
       </c>
-      <c r="F9" s="49" t="s">
+      <c r="F9" s="12" t="s">
         <v>24</v>
       </c>
       <c r="G9" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H9" s="59" t="s">
+      <c r="H9" s="55" t="s">
         <v>18</v>
       </c>
-      <c r="I9" s="54">
+      <c r="I9" s="51">
         <v>45925</v>
       </c>
     </row>
@@ -1266,22 +1401,22 @@
       <c r="C10" s="27">
         <v>45936</v>
       </c>
-      <c r="D10" s="46">
+      <c r="D10" s="24">
         <v>134654702</v>
       </c>
-      <c r="E10" s="51">
+      <c r="E10" s="49">
         <v>3450091832</v>
       </c>
-      <c r="F10" s="49" t="s">
+      <c r="F10" s="12" t="s">
         <v>25</v>
       </c>
       <c r="G10" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H10" s="56" t="s">
+      <c r="H10" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="I10" s="54">
+      <c r="I10" s="51">
         <v>45926</v>
       </c>
     </row>
@@ -1295,22 +1430,22 @@
       <c r="C11" s="27">
         <v>45936</v>
       </c>
-      <c r="D11" s="46">
+      <c r="D11" s="24">
         <v>134652102</v>
       </c>
-      <c r="E11" s="51">
+      <c r="E11" s="49">
         <v>3450091634</v>
       </c>
-      <c r="F11" s="49" t="s">
+      <c r="F11" s="12" t="s">
         <v>26</v>
       </c>
       <c r="G11" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="H11" s="56" t="s">
+      <c r="H11" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="I11" s="54">
+      <c r="I11" s="51">
         <v>45926</v>
       </c>
     </row>
@@ -1324,22 +1459,22 @@
       <c r="C12" s="27">
         <v>45936</v>
       </c>
-      <c r="D12" s="46">
+      <c r="D12" s="24">
         <v>134698414</v>
       </c>
-      <c r="E12" s="51">
+      <c r="E12" s="49">
         <v>3450090886</v>
       </c>
-      <c r="F12" s="49" t="s">
+      <c r="F12" s="12" t="s">
         <v>29</v>
       </c>
       <c r="G12" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="H12" s="55" t="s">
+      <c r="H12" s="52" t="s">
         <v>30</v>
       </c>
-      <c r="I12" s="54">
+      <c r="I12" s="51">
         <v>45936</v>
       </c>
     </row>
@@ -1353,22 +1488,22 @@
       <c r="C13" s="27">
         <v>45936</v>
       </c>
-      <c r="D13" s="46">
+      <c r="D13" s="24">
         <v>134701391</v>
       </c>
-      <c r="E13" s="51">
+      <c r="E13" s="49">
         <v>3450094692</v>
       </c>
-      <c r="F13" s="49" t="s">
+      <c r="F13" s="12" t="s">
         <v>31</v>
       </c>
       <c r="G13" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="H13" s="55" t="s">
+      <c r="H13" s="52" t="s">
         <v>32</v>
       </c>
-      <c r="I13" s="54">
+      <c r="I13" s="51">
         <v>45936</v>
       </c>
     </row>
@@ -1382,22 +1517,22 @@
       <c r="C14" s="27">
         <v>45936</v>
       </c>
-      <c r="D14" s="46">
+      <c r="D14" s="24">
         <v>134703116</v>
       </c>
-      <c r="E14" s="51">
+      <c r="E14" s="49">
         <v>3450094824</v>
       </c>
-      <c r="F14" s="49" t="s">
+      <c r="F14" s="12" t="s">
         <v>33</v>
       </c>
       <c r="G14" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="H14" s="55" t="s">
+      <c r="H14" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="I14" s="54">
+      <c r="I14" s="51">
         <v>45930</v>
       </c>
     </row>
@@ -1411,22 +1546,22 @@
       <c r="C15" s="27">
         <v>45936</v>
       </c>
-      <c r="D15" s="46">
+      <c r="D15" s="24">
         <v>134713267</v>
       </c>
-      <c r="E15" s="51">
+      <c r="E15" s="49">
         <v>3450095572</v>
       </c>
-      <c r="F15" s="49" t="s">
+      <c r="F15" s="12" t="s">
         <v>35</v>
       </c>
       <c r="G15" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="H15" s="56" t="s">
+      <c r="H15" s="52" t="s">
         <v>36</v>
       </c>
-      <c r="I15" s="54">
+      <c r="I15" s="51">
         <v>45930</v>
       </c>
     </row>
@@ -1440,22 +1575,22 @@
       <c r="C16" s="27">
         <v>45936</v>
       </c>
-      <c r="D16" s="46">
+      <c r="D16" s="24">
         <v>134681011</v>
       </c>
-      <c r="E16" s="51">
+      <c r="E16" s="49">
         <v>3450093438</v>
       </c>
-      <c r="F16" s="49" t="s">
+      <c r="F16" s="12" t="s">
         <v>37</v>
       </c>
       <c r="G16" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="H16" s="56" t="s">
+      <c r="H16" s="52" t="s">
         <v>39</v>
       </c>
-      <c r="I16" s="54">
+      <c r="I16" s="51">
         <v>45932</v>
       </c>
     </row>
@@ -1469,22 +1604,22 @@
       <c r="C17" s="27">
         <v>45936</v>
       </c>
-      <c r="D17" s="46">
+      <c r="D17" s="24">
         <v>134756714</v>
       </c>
-      <c r="E17" s="51">
+      <c r="E17" s="49">
         <v>3450098344</v>
       </c>
-      <c r="F17" s="49" t="s">
+      <c r="F17" s="12" t="s">
         <v>40</v>
       </c>
       <c r="G17" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="H17" s="56" t="s">
+      <c r="H17" s="52" t="s">
         <v>41</v>
       </c>
-      <c r="I17" s="54">
+      <c r="I17" s="51">
         <v>45903</v>
       </c>
     </row>
@@ -1498,22 +1633,22 @@
       <c r="C18" s="27">
         <v>45936</v>
       </c>
-      <c r="D18" s="46">
+      <c r="D18" s="24">
         <v>134770404</v>
       </c>
-      <c r="E18" s="51">
+      <c r="E18" s="49">
         <v>3450098828</v>
       </c>
-      <c r="F18" s="49" t="s">
+      <c r="F18" s="12" t="s">
         <v>42</v>
       </c>
       <c r="G18" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="H18" s="56" t="s">
+      <c r="H18" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="I18" s="54">
+      <c r="I18" s="51">
         <v>45933</v>
       </c>
     </row>
@@ -1527,22 +1662,22 @@
       <c r="C19" s="27">
         <v>45936</v>
       </c>
-      <c r="D19" s="46">
+      <c r="D19" s="24">
         <v>134598337</v>
       </c>
-      <c r="E19" s="51">
+      <c r="E19" s="49">
         <v>3450088367</v>
       </c>
-      <c r="F19" s="49" t="s">
+      <c r="F19" s="12" t="s">
         <v>43</v>
       </c>
       <c r="G19" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="H19" s="55" t="s">
+      <c r="H19" s="52" t="s">
         <v>45</v>
       </c>
-      <c r="I19" s="54">
+      <c r="I19" s="51">
         <v>45929</v>
       </c>
     </row>
@@ -1556,22 +1691,22 @@
       <c r="C20" s="27">
         <v>45936</v>
       </c>
-      <c r="D20" s="46">
+      <c r="D20" s="24">
         <v>134665384</v>
       </c>
-      <c r="E20" s="51">
+      <c r="E20" s="49">
         <v>3450092525</v>
       </c>
-      <c r="F20" s="49" t="s">
+      <c r="F20" s="12" t="s">
         <v>46</v>
       </c>
       <c r="G20" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="H20" s="56" t="s">
+      <c r="H20" s="52" t="s">
         <v>39</v>
       </c>
-      <c r="I20" s="54">
+      <c r="I20" s="51">
         <v>45930</v>
       </c>
     </row>
@@ -1585,22 +1720,22 @@
       <c r="C21" s="27">
         <v>45936</v>
       </c>
-      <c r="D21" s="46">
+      <c r="D21" s="24">
         <v>134662074</v>
       </c>
-      <c r="E21" s="51">
+      <c r="E21" s="49">
         <v>3450092371</v>
       </c>
-      <c r="F21" s="49" t="s">
+      <c r="F21" s="12" t="s">
         <v>47</v>
       </c>
       <c r="G21" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="H21" s="56" t="s">
+      <c r="H21" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="I21" s="54">
+      <c r="I21" s="51">
         <v>45926</v>
       </c>
     </row>
@@ -1614,22 +1749,22 @@
       <c r="C22" s="27">
         <v>45936</v>
       </c>
-      <c r="D22" s="48">
+      <c r="D22" s="47">
         <v>134660067</v>
       </c>
-      <c r="E22" s="51">
+      <c r="E22" s="49">
         <v>3450092261</v>
       </c>
-      <c r="F22" s="53" t="s">
+      <c r="F22" s="30" t="s">
         <v>48</v>
       </c>
       <c r="G22" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="H22" s="56" t="s">
+      <c r="H22" s="52" t="s">
         <v>39</v>
       </c>
-      <c r="I22" s="54">
+      <c r="I22" s="51">
         <v>45932</v>
       </c>
     </row>
@@ -1643,22 +1778,22 @@
       <c r="C23" s="27">
         <v>45936</v>
       </c>
-      <c r="D23" s="46">
+      <c r="D23" s="24">
         <v>134692267</v>
       </c>
-      <c r="E23" s="51">
+      <c r="E23" s="49">
         <v>3450094164</v>
       </c>
-      <c r="F23" s="49" t="s">
+      <c r="F23" s="12" t="s">
         <v>49</v>
       </c>
       <c r="G23" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="H23" s="56" t="s">
+      <c r="H23" s="52" t="s">
         <v>39</v>
       </c>
-      <c r="I23" s="54">
+      <c r="I23" s="51">
         <v>45932</v>
       </c>
     </row>
@@ -1672,22 +1807,22 @@
       <c r="C24" s="27">
         <v>45936</v>
       </c>
-      <c r="D24" s="46">
+      <c r="D24" s="24">
         <v>134651036</v>
       </c>
-      <c r="E24" s="51">
+      <c r="E24" s="49">
         <v>3450088895</v>
       </c>
-      <c r="F24" s="49" t="s">
+      <c r="F24" s="12" t="s">
         <v>50</v>
       </c>
       <c r="G24" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H24" s="56" t="s">
+      <c r="H24" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="I24" s="54">
+      <c r="I24" s="51">
         <v>45924</v>
       </c>
     </row>
@@ -1701,22 +1836,22 @@
       <c r="C25" s="27">
         <v>45936</v>
       </c>
-      <c r="D25" s="46">
+      <c r="D25" s="24">
         <v>134652142</v>
       </c>
-      <c r="E25" s="51">
+      <c r="E25" s="49">
         <v>3450091645</v>
       </c>
-      <c r="F25" s="49" t="s">
+      <c r="F25" s="12" t="s">
         <v>51</v>
       </c>
       <c r="G25" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H25" s="56" t="s">
+      <c r="H25" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="I25" s="54">
+      <c r="I25" s="51">
         <v>45926</v>
       </c>
     </row>
@@ -1730,22 +1865,22 @@
       <c r="C26" s="27">
         <v>45936</v>
       </c>
-      <c r="D26" s="46">
+      <c r="D26" s="24">
         <v>134652159</v>
       </c>
-      <c r="E26" s="51">
+      <c r="E26" s="49">
         <v>3450091656</v>
       </c>
-      <c r="F26" s="49" t="s">
+      <c r="F26" s="12" t="s">
         <v>52</v>
       </c>
       <c r="G26" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H26" s="56" t="s">
+      <c r="H26" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="I26" s="54">
+      <c r="I26" s="51">
         <v>45926</v>
       </c>
     </row>
@@ -1759,22 +1894,22 @@
       <c r="C27" s="27">
         <v>45936</v>
       </c>
-      <c r="D27" s="46">
+      <c r="D27" s="24">
         <v>134652965</v>
       </c>
-      <c r="E27" s="51">
+      <c r="E27" s="49">
         <v>3450091722</v>
       </c>
-      <c r="F27" s="49" t="s">
+      <c r="F27" s="12" t="s">
         <v>53</v>
       </c>
       <c r="G27" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H27" s="56" t="s">
+      <c r="H27" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="I27" s="54">
+      <c r="I27" s="51">
         <v>45926</v>
       </c>
     </row>
@@ -1788,22 +1923,22 @@
       <c r="C28" s="27">
         <v>45936</v>
       </c>
-      <c r="D28" s="46">
+      <c r="D28" s="24">
         <v>134655241</v>
       </c>
-      <c r="E28" s="51">
+      <c r="E28" s="49">
         <v>3450091876</v>
       </c>
-      <c r="F28" s="49" t="s">
+      <c r="F28" s="12" t="s">
         <v>54</v>
       </c>
       <c r="G28" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H28" s="56" t="s">
+      <c r="H28" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="I28" s="54">
+      <c r="I28" s="51">
         <v>45926</v>
       </c>
     </row>
@@ -1817,22 +1952,22 @@
       <c r="C29" s="27">
         <v>45936</v>
       </c>
-      <c r="D29" s="46">
+      <c r="D29" s="24">
         <v>134658334</v>
       </c>
-      <c r="E29" s="51">
+      <c r="E29" s="49">
         <v>3450092096</v>
       </c>
-      <c r="F29" s="49" t="s">
+      <c r="F29" s="12" t="s">
         <v>55</v>
       </c>
       <c r="G29" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H29" s="56" t="s">
+      <c r="H29" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="I29" s="54">
+      <c r="I29" s="51">
         <v>45926</v>
       </c>
     </row>
@@ -1846,22 +1981,22 @@
       <c r="C30" s="27">
         <v>45936</v>
       </c>
-      <c r="D30" s="46">
+      <c r="D30" s="24">
         <v>134658593</v>
       </c>
-      <c r="E30" s="51">
+      <c r="E30" s="49">
         <v>3450092118</v>
       </c>
-      <c r="F30" s="49" t="s">
+      <c r="F30" s="12" t="s">
         <v>56</v>
       </c>
       <c r="G30" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H30" s="56" t="s">
+      <c r="H30" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="I30" s="54">
+      <c r="I30" s="51">
         <v>45926</v>
       </c>
     </row>
@@ -1875,22 +2010,22 @@
       <c r="C31" s="27">
         <v>45936</v>
       </c>
-      <c r="D31" s="46">
+      <c r="D31" s="24">
         <v>134662051</v>
       </c>
-      <c r="E31" s="51">
+      <c r="E31" s="49">
         <v>3450092360</v>
       </c>
-      <c r="F31" s="49" t="s">
+      <c r="F31" s="12" t="s">
         <v>57</v>
       </c>
       <c r="G31" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H31" s="56" t="s">
+      <c r="H31" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="I31" s="54">
+      <c r="I31" s="51">
         <v>45926</v>
       </c>
     </row>
@@ -1904,22 +2039,22 @@
       <c r="C32" s="27">
         <v>45936</v>
       </c>
-      <c r="D32" s="46">
+      <c r="D32" s="24">
         <v>134665397</v>
       </c>
-      <c r="E32" s="51">
+      <c r="E32" s="49">
         <v>3450092536</v>
       </c>
-      <c r="F32" s="49" t="s">
+      <c r="F32" s="12" t="s">
         <v>58</v>
       </c>
       <c r="G32" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H32" s="56" t="s">
+      <c r="H32" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="I32" s="54">
+      <c r="I32" s="51">
         <v>45926</v>
       </c>
     </row>
@@ -1933,22 +2068,22 @@
       <c r="C33" s="27">
         <v>45936</v>
       </c>
-      <c r="D33" s="46">
+      <c r="D33" s="24">
         <v>134668994</v>
       </c>
-      <c r="E33" s="51">
+      <c r="E33" s="49">
         <v>3450092833</v>
       </c>
-      <c r="F33" s="49" t="s">
+      <c r="F33" s="12" t="s">
         <v>59</v>
       </c>
       <c r="G33" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H33" s="56" t="s">
+      <c r="H33" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="I33" s="54">
+      <c r="I33" s="51">
         <v>45926</v>
       </c>
     </row>
@@ -1962,22 +2097,22 @@
       <c r="C34" s="27">
         <v>45936</v>
       </c>
-      <c r="D34" s="46">
+      <c r="D34" s="24">
         <v>134669432</v>
       </c>
-      <c r="E34" s="51">
+      <c r="E34" s="49">
         <v>3450092899</v>
       </c>
-      <c r="F34" s="49" t="s">
+      <c r="F34" s="12" t="s">
         <v>60</v>
       </c>
       <c r="G34" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H34" s="56" t="s">
+      <c r="H34" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="I34" s="54">
+      <c r="I34" s="51">
         <v>45926</v>
       </c>
     </row>
@@ -1985,9 +2120,9 @@
       <c r="A35" s="6"/>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
-      <c r="D35" s="47"/>
+      <c r="D35" s="46"/>
       <c r="E35" s="18"/>
-      <c r="F35" s="52"/>
+      <c r="F35" s="50"/>
       <c r="G35" s="20"/>
       <c r="H35" s="9"/>
       <c r="I35" s="26"/>
@@ -2228,7 +2363,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFA17127-7620-4DD9-9061-6C654E2EC5C2}">
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -2275,362 +2410,848 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="26"/>
+      <c r="B2" s="7">
+        <v>45929</v>
+      </c>
+      <c r="C2" s="27">
+        <v>45937</v>
+      </c>
+      <c r="D2" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="E2" s="18">
+        <v>3450094362</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="H2" s="54" t="s">
+        <v>64</v>
+      </c>
+      <c r="I2" s="51"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="26"/>
+      <c r="B3" s="7">
+        <v>45934</v>
+      </c>
+      <c r="C3" s="27">
+        <v>45937</v>
+      </c>
+      <c r="D3" s="47" t="s">
+        <v>61</v>
+      </c>
+      <c r="E3" s="18">
+        <v>3450099444</v>
+      </c>
+      <c r="F3" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="G3" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="H3" s="52" t="s">
+        <v>66</v>
+      </c>
+      <c r="I3" s="51"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="26"/>
+      <c r="B4" s="7">
+        <v>45929</v>
+      </c>
+      <c r="C4" s="27">
+        <v>45937</v>
+      </c>
+      <c r="D4" s="24">
+        <v>134681507</v>
+      </c>
+      <c r="E4" s="18">
+        <v>3450093493</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" s="52" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" s="61">
+        <v>45929</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="26"/>
+      <c r="B5" s="7">
+        <v>45929</v>
+      </c>
+      <c r="C5" s="27">
+        <v>45937</v>
+      </c>
+      <c r="D5" s="24">
+        <v>134683357</v>
+      </c>
+      <c r="E5" s="18">
+        <v>3450093636</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" s="51">
+        <v>45929</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="26"/>
+      <c r="B6" s="7">
+        <v>45929</v>
+      </c>
+      <c r="C6" s="27">
+        <v>45937</v>
+      </c>
+      <c r="D6" s="24">
+        <v>134689189</v>
+      </c>
+      <c r="E6" s="18">
+        <v>3450093977</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="G6" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="57" t="s">
+        <v>18</v>
+      </c>
+      <c r="I6" s="51">
+        <v>45929</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="30"/>
-      <c r="I7" s="26"/>
+      <c r="B7" s="7">
+        <v>45929</v>
+      </c>
+      <c r="C7" s="27">
+        <v>45937</v>
+      </c>
+      <c r="D7" s="24">
+        <v>134691356</v>
+      </c>
+      <c r="E7" s="18">
+        <v>3450094098</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="G7" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7" s="54" t="s">
+        <v>18</v>
+      </c>
+      <c r="I7" s="51">
+        <v>45929</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="26"/>
+      <c r="B8" s="7">
+        <v>45929</v>
+      </c>
+      <c r="C8" s="27">
+        <v>45937</v>
+      </c>
+      <c r="D8" s="24">
+        <v>134691773</v>
+      </c>
+      <c r="E8" s="18">
+        <v>3450094120</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="G8" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" s="55" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" s="51">
+        <v>45929</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="24"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="26"/>
+      <c r="B9" s="7">
+        <v>45929</v>
+      </c>
+      <c r="C9" s="27">
+        <v>45937</v>
+      </c>
+      <c r="D9" s="24">
+        <v>134680144</v>
+      </c>
+      <c r="E9" s="18">
+        <v>3450093405</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="H9" s="55" t="s">
+        <v>73</v>
+      </c>
+      <c r="I9" s="58">
+        <v>45936</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="26"/>
+      <c r="B10" s="7">
+        <v>45930</v>
+      </c>
+      <c r="C10" s="27">
+        <v>45937</v>
+      </c>
+      <c r="D10" s="24">
+        <v>134711738</v>
+      </c>
+      <c r="E10" s="18">
+        <v>3450095396</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="G10" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H10" s="52" t="s">
+        <v>75</v>
+      </c>
+      <c r="I10" s="51">
+        <v>45930</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="26"/>
+      <c r="B11" s="7">
+        <v>45931</v>
+      </c>
+      <c r="C11" s="27">
+        <v>45937</v>
+      </c>
+      <c r="D11" s="24">
+        <v>134720385</v>
+      </c>
+      <c r="E11" s="18">
+        <v>3450096078</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H11" s="52" t="s">
+        <v>75</v>
+      </c>
+      <c r="I11" s="51">
+        <v>45931</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="26"/>
+      <c r="B12" s="7">
+        <v>45949</v>
+      </c>
+      <c r="C12" s="27">
+        <v>45937</v>
+      </c>
+      <c r="D12" s="24">
+        <v>134755230</v>
+      </c>
+      <c r="E12" s="18">
+        <v>3450098245</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H12" s="60" t="s">
+        <v>78</v>
+      </c>
+      <c r="I12" s="51">
+        <v>45937</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="26"/>
+      <c r="B13" s="7">
+        <v>45933</v>
+      </c>
+      <c r="C13" s="27">
+        <v>45937</v>
+      </c>
+      <c r="D13" s="24">
+        <v>134775095</v>
+      </c>
+      <c r="E13" s="18">
+        <v>3450099081</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="H13" s="60" t="s">
+        <v>73</v>
+      </c>
+      <c r="I13" s="51">
+        <v>45936</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="26"/>
+      <c r="B14" s="7">
+        <v>45933</v>
+      </c>
+      <c r="C14" s="27">
+        <v>45937</v>
+      </c>
+      <c r="D14" s="24">
+        <v>134772972</v>
+      </c>
+      <c r="E14" s="18">
+        <v>3450098971</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="G14" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H14" s="52" t="s">
+        <v>20</v>
+      </c>
+      <c r="I14" s="51">
+        <v>45933</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="26"/>
+      <c r="B15" s="7">
+        <v>45933</v>
+      </c>
+      <c r="C15" s="27">
+        <v>45937</v>
+      </c>
+      <c r="D15" s="24">
+        <v>134770331</v>
+      </c>
+      <c r="E15" s="18">
+        <v>3450098795</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="G15" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H15" s="52" t="s">
+        <v>20</v>
+      </c>
+      <c r="I15" s="51">
+        <v>45933</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="26"/>
+      <c r="B16" s="7">
+        <v>45932</v>
+      </c>
+      <c r="C16" s="27">
+        <v>45937</v>
+      </c>
+      <c r="D16" s="24">
+        <v>134757544</v>
+      </c>
+      <c r="E16" s="18">
+        <v>3450098400</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="H16" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="I16" s="51">
+        <v>45936</v>
+      </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="26"/>
+      <c r="B17" s="7">
+        <v>45931</v>
+      </c>
+      <c r="C17" s="27">
+        <v>45937</v>
+      </c>
+      <c r="D17" s="24">
+        <v>134623063</v>
+      </c>
+      <c r="E17" s="18">
+        <v>3450090116</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="G17" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H17" s="60" t="s">
+        <v>83</v>
+      </c>
+      <c r="I17" s="51">
+        <v>45926</v>
+      </c>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="6"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="27"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="26"/>
+      <c r="A18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="7">
+        <v>45926</v>
+      </c>
+      <c r="C18" s="27">
+        <v>45937</v>
+      </c>
+      <c r="D18" s="24">
+        <v>134680848</v>
+      </c>
+      <c r="E18" s="18">
+        <v>3450092954</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="G18" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="H18" s="52" t="s">
+        <v>18</v>
+      </c>
+      <c r="I18" s="51">
+        <v>45926</v>
+      </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="6"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="26"/>
+      <c r="A19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="7">
+        <v>45929</v>
+      </c>
+      <c r="C19" s="27">
+        <v>45937</v>
+      </c>
+      <c r="D19" s="24">
+        <v>134681098</v>
+      </c>
+      <c r="E19" s="18">
+        <v>3450093450</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="G19" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="H19" s="52" t="s">
+        <v>18</v>
+      </c>
+      <c r="I19" s="51">
+        <v>45929</v>
+      </c>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="6"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="27"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="26"/>
+      <c r="A20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="7">
+        <v>45929</v>
+      </c>
+      <c r="C20" s="27">
+        <v>45937</v>
+      </c>
+      <c r="D20" s="24">
+        <v>134683463</v>
+      </c>
+      <c r="E20" s="18">
+        <v>3450093658</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="H20" s="52" t="s">
+        <v>18</v>
+      </c>
+      <c r="I20" s="58">
+        <v>45929</v>
+      </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="6"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="27"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="26"/>
+      <c r="A21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="7">
+        <v>45929</v>
+      </c>
+      <c r="C21" s="27">
+        <v>45937</v>
+      </c>
+      <c r="D21" s="24">
+        <v>134684719</v>
+      </c>
+      <c r="E21" s="18">
+        <v>3450093713</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="G21" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="H21" s="52" t="s">
+        <v>18</v>
+      </c>
+      <c r="I21" s="51">
+        <v>45929</v>
+      </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="6"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="27"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="26"/>
+      <c r="A22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="7">
+        <v>45929</v>
+      </c>
+      <c r="C22" s="27">
+        <v>45937</v>
+      </c>
+      <c r="D22" s="24">
+        <v>134679649</v>
+      </c>
+      <c r="E22" s="18">
+        <v>3450093372</v>
+      </c>
+      <c r="F22" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="G22" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="H22" s="52" t="s">
+        <v>39</v>
+      </c>
+      <c r="I22" s="51">
+        <v>45936</v>
+      </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="6"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="24"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="26"/>
+      <c r="A23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="7">
+        <v>45929</v>
+      </c>
+      <c r="C23" s="27">
+        <v>45937</v>
+      </c>
+      <c r="D23" s="24">
+        <v>134687908</v>
+      </c>
+      <c r="E23" s="18">
+        <v>3450093878</v>
+      </c>
+      <c r="F23" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="G23" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="H23" s="52" t="s">
+        <v>18</v>
+      </c>
+      <c r="I23" s="51">
+        <v>45929</v>
+      </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="6"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="27"/>
-      <c r="D24" s="24"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="26"/>
+      <c r="A24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="7">
+        <v>45929</v>
+      </c>
+      <c r="C24" s="27">
+        <v>45937</v>
+      </c>
+      <c r="D24" s="24">
+        <v>134688236</v>
+      </c>
+      <c r="E24" s="18">
+        <v>3450093890</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="G24" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="H24" s="52" t="s">
+        <v>18</v>
+      </c>
+      <c r="I24" s="51">
+        <v>45929</v>
+      </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="6"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="24"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="26"/>
+      <c r="A25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="7">
+        <v>45929</v>
+      </c>
+      <c r="C25" s="27">
+        <v>45937</v>
+      </c>
+      <c r="D25" s="24">
+        <v>134688982</v>
+      </c>
+      <c r="E25" s="18">
+        <v>3450093966</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="G25" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="H25" s="59" t="s">
+        <v>18</v>
+      </c>
+      <c r="I25" s="51">
+        <v>45929</v>
+      </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="6"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="27"/>
-      <c r="D26" s="24"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="31"/>
-      <c r="I26" s="26"/>
+      <c r="A26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="7">
+        <v>45929</v>
+      </c>
+      <c r="C26" s="27">
+        <v>45937</v>
+      </c>
+      <c r="D26" s="24">
+        <v>134689719</v>
+      </c>
+      <c r="E26" s="18">
+        <v>3450094000</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="G26" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="H26" s="52" t="s">
+        <v>18</v>
+      </c>
+      <c r="I26" s="51">
+        <v>45929</v>
+      </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="6"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="27"/>
-      <c r="D27" s="24"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="26"/>
+      <c r="A27" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="7">
+        <v>45929</v>
+      </c>
+      <c r="C27" s="27">
+        <v>45937</v>
+      </c>
+      <c r="D27" s="24">
+        <v>134689748</v>
+      </c>
+      <c r="E27" s="18">
+        <v>3450094021</v>
+      </c>
+      <c r="F27" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="G27" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="H27" s="52" t="s">
+        <v>18</v>
+      </c>
+      <c r="I27" s="51">
+        <v>45929</v>
+      </c>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="6"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="27"/>
-      <c r="D28" s="24"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="26"/>
+      <c r="A28" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="7">
+        <v>45929</v>
+      </c>
+      <c r="C28" s="27">
+        <v>45937</v>
+      </c>
+      <c r="D28" s="24">
+        <v>134692186</v>
+      </c>
+      <c r="E28" s="18">
+        <v>3450094153</v>
+      </c>
+      <c r="F28" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="G28" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="H28" s="52" t="s">
+        <v>18</v>
+      </c>
+      <c r="I28" s="51">
+        <v>45929</v>
+      </c>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="6"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="24"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="26"/>
+      <c r="A29" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="7">
+        <v>45929</v>
+      </c>
+      <c r="C29" s="27">
+        <v>45937</v>
+      </c>
+      <c r="D29" s="24">
+        <v>134694208</v>
+      </c>
+      <c r="E29" s="18">
+        <v>3450094329</v>
+      </c>
+      <c r="F29" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="G29" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="H29" s="52" t="s">
+        <v>18</v>
+      </c>
+      <c r="I29" s="51">
+        <v>45929</v>
+      </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="6"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="27"/>
-      <c r="D30" s="24"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="20"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="26"/>
+      <c r="A30" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="7">
+        <v>45953</v>
+      </c>
+      <c r="C30" s="27">
+        <v>45937</v>
+      </c>
+      <c r="D30" s="24">
+        <v>134621154</v>
+      </c>
+      <c r="E30" s="18">
+        <v>3450089940</v>
+      </c>
+      <c r="F30" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="G30" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H30" s="60" t="s">
+        <v>97</v>
+      </c>
+      <c r="I30" s="51">
+        <v>45926</v>
+      </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="6"/>
       <c r="B31" s="7"/>
       <c r="C31" s="27"/>
-      <c r="D31" s="24"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="12"/>
+      <c r="D31" s="46"/>
+      <c r="E31" s="56"/>
+      <c r="F31" s="35"/>
       <c r="G31" s="20"/>
-      <c r="H31" s="9"/>
+      <c r="H31" s="31"/>
       <c r="I31" s="26"/>
     </row>
     <row r="32" spans="1:9">
@@ -2646,12 +3267,12 @@
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="6"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="27"/>
-      <c r="D33" s="24"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="20"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="22"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="6"/>
       <c r="H33" s="9"/>
       <c r="I33" s="26"/>
     </row>
@@ -2659,9 +3280,9 @@
       <c r="A34" s="6"/>
       <c r="B34" s="8"/>
       <c r="C34" s="7"/>
-      <c r="D34" s="22"/>
-      <c r="E34" s="22"/>
-      <c r="F34" s="15"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="9"/>
       <c r="G34" s="6"/>
       <c r="H34" s="9"/>
       <c r="I34" s="26"/>
@@ -2686,7 +3307,7 @@
       <c r="F36" s="9"/>
       <c r="G36" s="6"/>
       <c r="H36" s="9"/>
-      <c r="I36" s="26"/>
+      <c r="I36"/>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="6"/>
@@ -2886,28 +3507,17 @@
       <c r="H54" s="9"/>
       <c r="I54"/>
     </row>
-    <row r="55" spans="1:9">
-      <c r="A55" s="6"/>
-      <c r="B55" s="8"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="6"/>
-      <c r="H55" s="9"/>
-      <c r="I55"/>
-    </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="2">
+    <cfRule type="notContainsBlanks" priority="5">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A33" xr:uid="{4D257AA8-3FDB-42B7-A450-B3788B0ABB12}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A32" xr:uid="{4D257AA8-3FDB-42B7-A450-B3788B0ABB12}">
       <formula1>$J$2</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G41" xr:uid="{5FAA0C61-6912-46B8-8149-B719594B77CB}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G40" xr:uid="{5FAA0C61-6912-46B8-8149-B719594B77CB}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6031,56 +6641,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="44" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ac14f8cb44178d381f4c0afb30680a90">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5e58414b065c9b590c40efa77cd84bb6" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -6458,7 +7018,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-496593</_dlc_DocId>
@@ -6501,7 +7061,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -6510,18 +7070,68 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32450128-80FB-4462-BDF1-414021F91FB7}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E24C30B0-1A17-4BA3-9198-56DDF64907CD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas 06.10.2025 a 12.10.2025.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas 06.10.2025 a 12.10.2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms.sharepoint.com/teams/BR0010-4356589/Shared Documents/BACK-OFFICE SME/Santander/2025/Relatório de Recusas/05. Maio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9F0B08FA-2AEC-481E-9269-AC6335524428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{043F0B9B-CCFD-48B2-886B-736816539870}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="06.10" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="130">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -356,12 +356,120 @@
     <t>Favor enviar cópia completa da apólice referente 2024/2025 (Não
 será aceito a CI, uma vez em que a CBE não retorna os dados)</t>
   </si>
+  <si>
+    <t xml:space="preserve">FRANCISCO RODOLFO DA SILVA PAZ               </t>
+  </si>
+  <si>
+    <t>F
+avor enviar cópia completa da apólice anterior 2024/2025 (atual) a
+través desse e-mail. (Não será aceito a CI,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GISELE DE SOUZA RAMOS                        </t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 07.10.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JARDEL SOUSA CASTANHEIRA COSTA               </t>
+  </si>
+  <si>
+    <t>FRUSTRADO, FOTOS NÃO CORRIGIDAS: Frente e lateral do passageiro e lateral do motorista, Traseira e lateral do motorista, E do passageiro, Motor, Painel com carro ligado, Chassi, Porta malas</t>
+  </si>
+  <si>
+    <t>DOIS IRMAOS CONSTRUCOES E PREMOLDADOS LTDA ME</t>
+  </si>
+  <si>
+    <t>RECUSA: FRUSTRADO PRAZO EXPIRADO * SEGURADO NÃO CORRIGIU OS PASSOS SOLICITADOS Fotos que tiveram repique: Documento da moto, Painel com a motocicleta desli;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANTONIO SAMUEL MARCELINO                     </t>
+  </si>
+  <si>
+    <t>FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: PAINEL COM A MOTO LIGADA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JURANDIR MORAIS DA SILVA                     </t>
+  </si>
+  <si>
+    <t>PRAZO EXPIRADO/ FOTOS NAO CORRIGIDAS: HODOMETRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DARCI DA ROCHA RODRIGUES                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AIRES SOUZA MACIEL ME                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRA VITORIA BRUNA ESTETICA AVANCADA LTDA ME  </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que não
+há possibilidade efetuar a transferência de bônus para a empresa D
+RA VITORIA BRUNA ESTETICA AVANCADA LTD, pois o(a) senhor(a) ELIANE
+DOS SANTOS MOREIRA, não consta no quadro de sócios da empresa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DANIEL BARROS COSTA                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Constatamos que o modelo do veículo informado na cotação difere do
+constado, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">THIAGO ANDRADE PORTO                         </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que a
+apólice consta ativa na congênere, para que possamos prosseguir
+coma liberação do bloqueio será necessário a apresentação do en
+dosso de cancelamento emitido, a atualização junto a Central de Bô
+nus.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIMONE GRIMALDE CESAR HERINGER               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROSELIA APARECIDA GRANDE CARVALHO            </t>
+  </si>
+  <si>
+    <t>FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: Frente e lateral do passageiro, Frente e lateral do motorista, Painel com carro ligado, Chassi, Porta malas aberto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISIS CASTRO MARELLA ANDRE                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">F
+avor enviar cópia completa da apólice anterior 2024/2025 (atual) a
+través desse e-mail. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HUGO RENATO RAMOS FEITOSA                    </t>
+  </si>
+  <si>
+    <t>PRAZO EXPIRADO FOTO DO HODOMETRO Justificativa de Dados Divergentes: PRAZO EXPIRADO FOTO DO HODOMETRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEUSA ELI FIGUEREDO CERUTTI                  </t>
+  </si>
+  <si>
+    <t>Fotos que tiveram repique: Chassi Justificativa de Dados Divergentes: Fotos que tiveram repique: Chassi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANTONIO CARLOS RIBEIRO                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUZI MYKELLER BARBOSA DE MIRANDA             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIVIA PIRILLO GRECCHI                        </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -398,6 +506,13 @@
       <color theme="1"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF414141"/>
+      <name val="Allianz Neo"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -413,7 +528,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -630,12 +745,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -685,7 +813,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -778,8 +905,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1166,13 +1302,13 @@
       <c r="B2" s="7">
         <v>45923</v>
       </c>
-      <c r="C2" s="27">
+      <c r="C2" s="26">
         <v>45936</v>
       </c>
-      <c r="D2" s="24">
+      <c r="D2" s="23">
         <v>134596935</v>
       </c>
-      <c r="E2" s="48">
+      <c r="E2" s="47">
         <v>3450088180</v>
       </c>
       <c r="F2" s="12" t="s">
@@ -1181,10 +1317,10 @@
       <c r="G2" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="52" t="s">
+      <c r="H2" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="51">
+      <c r="I2" s="50">
         <v>45929</v>
       </c>
     </row>
@@ -1195,13 +1331,13 @@
       <c r="B3" s="7">
         <v>45926</v>
       </c>
-      <c r="C3" s="27">
+      <c r="C3" s="26">
         <v>45936</v>
       </c>
-      <c r="D3" s="24">
+      <c r="D3" s="23">
         <v>134652343</v>
       </c>
-      <c r="E3" s="49">
+      <c r="E3" s="48">
         <v>3450091667</v>
       </c>
       <c r="F3" s="12" t="s">
@@ -1210,10 +1346,10 @@
       <c r="G3" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="52" t="s">
+      <c r="H3" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="51">
+      <c r="I3" s="50">
         <v>45926</v>
       </c>
     </row>
@@ -1224,13 +1360,13 @@
       <c r="B4" s="7">
         <v>45926</v>
       </c>
-      <c r="C4" s="27">
+      <c r="C4" s="26">
         <v>45936</v>
       </c>
-      <c r="D4" s="24">
+      <c r="D4" s="23">
         <v>134658870</v>
       </c>
-      <c r="E4" s="49">
+      <c r="E4" s="48">
         <v>3450092130</v>
       </c>
       <c r="F4" s="12" t="s">
@@ -1239,10 +1375,10 @@
       <c r="G4" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="52" t="s">
+      <c r="H4" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="51">
+      <c r="I4" s="50">
         <v>45926</v>
       </c>
     </row>
@@ -1253,13 +1389,13 @@
       <c r="B5" s="7">
         <v>45926</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="26">
         <v>45936</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="23">
         <v>134667095</v>
       </c>
-      <c r="E5" s="49">
+      <c r="E5" s="48">
         <v>3450092712</v>
       </c>
       <c r="F5" s="12" t="s">
@@ -1268,10 +1404,10 @@
       <c r="G5" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="52" t="s">
+      <c r="H5" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="I5" s="51">
+      <c r="I5" s="50">
         <v>45926</v>
       </c>
     </row>
@@ -1282,13 +1418,13 @@
       <c r="B6" s="7">
         <v>45923</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="26">
         <v>45936</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="23">
         <v>134671678</v>
       </c>
-      <c r="E6" s="49">
+      <c r="E6" s="48">
         <v>3450087498</v>
       </c>
       <c r="F6" s="12" t="s">
@@ -1297,10 +1433,10 @@
       <c r="G6" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="53" t="s">
+      <c r="H6" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="I6" s="51">
+      <c r="I6" s="50">
         <v>45923</v>
       </c>
     </row>
@@ -1311,25 +1447,25 @@
       <c r="B7" s="7">
         <v>45926</v>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="26">
         <v>45936</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="23">
         <v>134665477</v>
       </c>
-      <c r="E7" s="49">
+      <c r="E7" s="48">
         <v>3450092547</v>
       </c>
       <c r="F7" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="G7" s="25" t="s">
+      <c r="G7" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="H7" s="54" t="s">
+      <c r="H7" s="53" t="s">
         <v>18</v>
       </c>
-      <c r="I7" s="51">
+      <c r="I7" s="50">
         <v>45926</v>
       </c>
     </row>
@@ -1340,25 +1476,25 @@
       <c r="B8" s="7">
         <v>45926</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="26">
         <v>45936</v>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="23">
         <v>134652012</v>
       </c>
-      <c r="E8" s="49">
+      <c r="E8" s="48">
         <v>3450091601</v>
       </c>
       <c r="F8" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="G8" s="25" t="s">
+      <c r="G8" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="H8" s="54" t="s">
+      <c r="H8" s="53" t="s">
         <v>18</v>
       </c>
-      <c r="I8" s="51">
+      <c r="I8" s="50">
         <v>45926</v>
       </c>
     </row>
@@ -1369,13 +1505,13 @@
       <c r="B9" s="7">
         <v>45925</v>
       </c>
-      <c r="C9" s="27">
+      <c r="C9" s="26">
         <v>45936</v>
       </c>
-      <c r="D9" s="24">
+      <c r="D9" s="23">
         <v>134656283</v>
       </c>
-      <c r="E9" s="49">
+      <c r="E9" s="48">
         <v>3450090875</v>
       </c>
       <c r="F9" s="12" t="s">
@@ -1384,10 +1520,10 @@
       <c r="G9" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H9" s="55" t="s">
+      <c r="H9" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="I9" s="51">
+      <c r="I9" s="50">
         <v>45925</v>
       </c>
     </row>
@@ -1398,13 +1534,13 @@
       <c r="B10" s="7">
         <v>45926</v>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="26">
         <v>45936</v>
       </c>
-      <c r="D10" s="24">
+      <c r="D10" s="23">
         <v>134654702</v>
       </c>
-      <c r="E10" s="49">
+      <c r="E10" s="48">
         <v>3450091832</v>
       </c>
       <c r="F10" s="12" t="s">
@@ -1413,10 +1549,10 @@
       <c r="G10" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H10" s="52" t="s">
+      <c r="H10" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="I10" s="51">
+      <c r="I10" s="50">
         <v>45926</v>
       </c>
     </row>
@@ -1427,13 +1563,13 @@
       <c r="B11" s="7">
         <v>45926</v>
       </c>
-      <c r="C11" s="27">
+      <c r="C11" s="26">
         <v>45936</v>
       </c>
-      <c r="D11" s="24">
+      <c r="D11" s="23">
         <v>134652102</v>
       </c>
-      <c r="E11" s="49">
+      <c r="E11" s="48">
         <v>3450091634</v>
       </c>
       <c r="F11" s="12" t="s">
@@ -1442,10 +1578,10 @@
       <c r="G11" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="H11" s="52" t="s">
+      <c r="H11" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="I11" s="51">
+      <c r="I11" s="50">
         <v>45926</v>
       </c>
     </row>
@@ -1456,13 +1592,13 @@
       <c r="B12" s="7">
         <v>45925</v>
       </c>
-      <c r="C12" s="27">
+      <c r="C12" s="26">
         <v>45936</v>
       </c>
-      <c r="D12" s="24">
+      <c r="D12" s="23">
         <v>134698414</v>
       </c>
-      <c r="E12" s="49">
+      <c r="E12" s="48">
         <v>3450090886</v>
       </c>
       <c r="F12" s="12" t="s">
@@ -1471,10 +1607,10 @@
       <c r="G12" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="H12" s="52" t="s">
+      <c r="H12" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="I12" s="51">
+      <c r="I12" s="50">
         <v>45936</v>
       </c>
     </row>
@@ -1485,13 +1621,13 @@
       <c r="B13" s="7">
         <v>45930</v>
       </c>
-      <c r="C13" s="27">
+      <c r="C13" s="26">
         <v>45936</v>
       </c>
-      <c r="D13" s="24">
+      <c r="D13" s="23">
         <v>134701391</v>
       </c>
-      <c r="E13" s="49">
+      <c r="E13" s="48">
         <v>3450094692</v>
       </c>
       <c r="F13" s="12" t="s">
@@ -1500,10 +1636,10 @@
       <c r="G13" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="H13" s="52" t="s">
+      <c r="H13" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="I13" s="51">
+      <c r="I13" s="50">
         <v>45936</v>
       </c>
     </row>
@@ -1514,13 +1650,13 @@
       <c r="B14" s="7">
         <v>45930</v>
       </c>
-      <c r="C14" s="27">
+      <c r="C14" s="26">
         <v>45936</v>
       </c>
-      <c r="D14" s="24">
+      <c r="D14" s="23">
         <v>134703116</v>
       </c>
-      <c r="E14" s="49">
+      <c r="E14" s="48">
         <v>3450094824</v>
       </c>
       <c r="F14" s="12" t="s">
@@ -1529,10 +1665,10 @@
       <c r="G14" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="H14" s="52" t="s">
+      <c r="H14" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="I14" s="51">
+      <c r="I14" s="50">
         <v>45930</v>
       </c>
     </row>
@@ -1543,13 +1679,13 @@
       <c r="B15" s="7">
         <v>45930</v>
       </c>
-      <c r="C15" s="27">
+      <c r="C15" s="26">
         <v>45936</v>
       </c>
-      <c r="D15" s="24">
+      <c r="D15" s="23">
         <v>134713267</v>
       </c>
-      <c r="E15" s="49">
+      <c r="E15" s="48">
         <v>3450095572</v>
       </c>
       <c r="F15" s="12" t="s">
@@ -1558,10 +1694,10 @@
       <c r="G15" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="H15" s="52" t="s">
+      <c r="H15" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="I15" s="51">
+      <c r="I15" s="50">
         <v>45930</v>
       </c>
     </row>
@@ -1572,13 +1708,13 @@
       <c r="B16" s="7">
         <v>45934</v>
       </c>
-      <c r="C16" s="27">
+      <c r="C16" s="26">
         <v>45936</v>
       </c>
-      <c r="D16" s="24">
+      <c r="D16" s="23">
         <v>134681011</v>
       </c>
-      <c r="E16" s="49">
+      <c r="E16" s="48">
         <v>3450093438</v>
       </c>
       <c r="F16" s="12" t="s">
@@ -1587,10 +1723,10 @@
       <c r="G16" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="H16" s="52" t="s">
+      <c r="H16" s="51" t="s">
         <v>39</v>
       </c>
-      <c r="I16" s="51">
+      <c r="I16" s="50">
         <v>45932</v>
       </c>
     </row>
@@ -1601,13 +1737,13 @@
       <c r="B17" s="7">
         <v>45932</v>
       </c>
-      <c r="C17" s="27">
+      <c r="C17" s="26">
         <v>45936</v>
       </c>
-      <c r="D17" s="24">
+      <c r="D17" s="23">
         <v>134756714</v>
       </c>
-      <c r="E17" s="49">
+      <c r="E17" s="48">
         <v>3450098344</v>
       </c>
       <c r="F17" s="12" t="s">
@@ -1616,10 +1752,10 @@
       <c r="G17" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="H17" s="52" t="s">
+      <c r="H17" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="I17" s="51">
+      <c r="I17" s="50">
         <v>45903</v>
       </c>
     </row>
@@ -1630,13 +1766,13 @@
       <c r="B18" s="7">
         <v>45933</v>
       </c>
-      <c r="C18" s="27">
+      <c r="C18" s="26">
         <v>45936</v>
       </c>
-      <c r="D18" s="24">
+      <c r="D18" s="23">
         <v>134770404</v>
       </c>
-      <c r="E18" s="49">
+      <c r="E18" s="48">
         <v>3450098828</v>
       </c>
       <c r="F18" s="12" t="s">
@@ -1645,10 +1781,10 @@
       <c r="G18" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="H18" s="52" t="s">
+      <c r="H18" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="I18" s="51">
+      <c r="I18" s="50">
         <v>45933</v>
       </c>
     </row>
@@ -1659,13 +1795,13 @@
       <c r="B19" s="7">
         <v>45923</v>
       </c>
-      <c r="C19" s="27">
+      <c r="C19" s="26">
         <v>45936</v>
       </c>
-      <c r="D19" s="24">
+      <c r="D19" s="23">
         <v>134598337</v>
       </c>
-      <c r="E19" s="49">
+      <c r="E19" s="48">
         <v>3450088367</v>
       </c>
       <c r="F19" s="12" t="s">
@@ -1674,10 +1810,10 @@
       <c r="G19" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="H19" s="52" t="s">
+      <c r="H19" s="51" t="s">
         <v>45</v>
       </c>
-      <c r="I19" s="51">
+      <c r="I19" s="50">
         <v>45929</v>
       </c>
     </row>
@@ -1688,13 +1824,13 @@
       <c r="B20" s="7">
         <v>45933</v>
       </c>
-      <c r="C20" s="27">
+      <c r="C20" s="26">
         <v>45936</v>
       </c>
-      <c r="D20" s="24">
+      <c r="D20" s="23">
         <v>134665384</v>
       </c>
-      <c r="E20" s="49">
+      <c r="E20" s="48">
         <v>3450092525</v>
       </c>
       <c r="F20" s="12" t="s">
@@ -1703,10 +1839,10 @@
       <c r="G20" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="H20" s="52" t="s">
+      <c r="H20" s="51" t="s">
         <v>39</v>
       </c>
-      <c r="I20" s="51">
+      <c r="I20" s="50">
         <v>45930</v>
       </c>
     </row>
@@ -1717,13 +1853,13 @@
       <c r="B21" s="7">
         <v>45926</v>
       </c>
-      <c r="C21" s="27">
+      <c r="C21" s="26">
         <v>45936</v>
       </c>
-      <c r="D21" s="24">
+      <c r="D21" s="23">
         <v>134662074</v>
       </c>
-      <c r="E21" s="49">
+      <c r="E21" s="48">
         <v>3450092371</v>
       </c>
       <c r="F21" s="12" t="s">
@@ -1732,10 +1868,10 @@
       <c r="G21" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="H21" s="52" t="s">
+      <c r="H21" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="I21" s="51">
+      <c r="I21" s="50">
         <v>45926</v>
       </c>
     </row>
@@ -1746,25 +1882,25 @@
       <c r="B22" s="7">
         <v>45928</v>
       </c>
-      <c r="C22" s="27">
+      <c r="C22" s="26">
         <v>45936</v>
       </c>
-      <c r="D22" s="47">
+      <c r="D22" s="46">
         <v>134660067</v>
       </c>
-      <c r="E22" s="49">
+      <c r="E22" s="48">
         <v>3450092261</v>
       </c>
-      <c r="F22" s="30" t="s">
+      <c r="F22" s="29" t="s">
         <v>48</v>
       </c>
       <c r="G22" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="H22" s="52" t="s">
+      <c r="H22" s="51" t="s">
         <v>39</v>
       </c>
-      <c r="I22" s="51">
+      <c r="I22" s="50">
         <v>45932</v>
       </c>
     </row>
@@ -1775,13 +1911,13 @@
       <c r="B23" s="7">
         <v>45946</v>
       </c>
-      <c r="C23" s="27">
+      <c r="C23" s="26">
         <v>45936</v>
       </c>
-      <c r="D23" s="24">
+      <c r="D23" s="23">
         <v>134692267</v>
       </c>
-      <c r="E23" s="49">
+      <c r="E23" s="48">
         <v>3450094164</v>
       </c>
       <c r="F23" s="12" t="s">
@@ -1790,10 +1926,10 @@
       <c r="G23" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="H23" s="52" t="s">
+      <c r="H23" s="51" t="s">
         <v>39</v>
       </c>
-      <c r="I23" s="51">
+      <c r="I23" s="50">
         <v>45932</v>
       </c>
     </row>
@@ -1804,13 +1940,13 @@
       <c r="B24" s="7">
         <v>45924</v>
       </c>
-      <c r="C24" s="27">
+      <c r="C24" s="26">
         <v>45936</v>
       </c>
-      <c r="D24" s="24">
+      <c r="D24" s="23">
         <v>134651036</v>
       </c>
-      <c r="E24" s="49">
+      <c r="E24" s="48">
         <v>3450088895</v>
       </c>
       <c r="F24" s="12" t="s">
@@ -1819,10 +1955,10 @@
       <c r="G24" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H24" s="52" t="s">
+      <c r="H24" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="I24" s="51">
+      <c r="I24" s="50">
         <v>45924</v>
       </c>
     </row>
@@ -1833,13 +1969,13 @@
       <c r="B25" s="7">
         <v>45926</v>
       </c>
-      <c r="C25" s="27">
+      <c r="C25" s="26">
         <v>45936</v>
       </c>
-      <c r="D25" s="24">
+      <c r="D25" s="23">
         <v>134652142</v>
       </c>
-      <c r="E25" s="49">
+      <c r="E25" s="48">
         <v>3450091645</v>
       </c>
       <c r="F25" s="12" t="s">
@@ -1848,10 +1984,10 @@
       <c r="G25" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H25" s="52" t="s">
+      <c r="H25" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="I25" s="51">
+      <c r="I25" s="50">
         <v>45926</v>
       </c>
     </row>
@@ -1862,13 +1998,13 @@
       <c r="B26" s="7">
         <v>45926</v>
       </c>
-      <c r="C26" s="27">
+      <c r="C26" s="26">
         <v>45936</v>
       </c>
-      <c r="D26" s="24">
+      <c r="D26" s="23">
         <v>134652159</v>
       </c>
-      <c r="E26" s="49">
+      <c r="E26" s="48">
         <v>3450091656</v>
       </c>
       <c r="F26" s="12" t="s">
@@ -1877,10 +2013,10 @@
       <c r="G26" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H26" s="52" t="s">
+      <c r="H26" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="I26" s="51">
+      <c r="I26" s="50">
         <v>45926</v>
       </c>
     </row>
@@ -1891,13 +2027,13 @@
       <c r="B27" s="7">
         <v>45926</v>
       </c>
-      <c r="C27" s="27">
+      <c r="C27" s="26">
         <v>45936</v>
       </c>
-      <c r="D27" s="24">
+      <c r="D27" s="23">
         <v>134652965</v>
       </c>
-      <c r="E27" s="49">
+      <c r="E27" s="48">
         <v>3450091722</v>
       </c>
       <c r="F27" s="12" t="s">
@@ -1906,10 +2042,10 @@
       <c r="G27" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H27" s="52" t="s">
+      <c r="H27" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="I27" s="51">
+      <c r="I27" s="50">
         <v>45926</v>
       </c>
     </row>
@@ -1920,13 +2056,13 @@
       <c r="B28" s="7">
         <v>45926</v>
       </c>
-      <c r="C28" s="27">
+      <c r="C28" s="26">
         <v>45936</v>
       </c>
-      <c r="D28" s="24">
+      <c r="D28" s="23">
         <v>134655241</v>
       </c>
-      <c r="E28" s="49">
+      <c r="E28" s="48">
         <v>3450091876</v>
       </c>
       <c r="F28" s="12" t="s">
@@ -1935,10 +2071,10 @@
       <c r="G28" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H28" s="52" t="s">
+      <c r="H28" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="I28" s="51">
+      <c r="I28" s="50">
         <v>45926</v>
       </c>
     </row>
@@ -1949,13 +2085,13 @@
       <c r="B29" s="7">
         <v>45926</v>
       </c>
-      <c r="C29" s="27">
+      <c r="C29" s="26">
         <v>45936</v>
       </c>
-      <c r="D29" s="24">
+      <c r="D29" s="23">
         <v>134658334</v>
       </c>
-      <c r="E29" s="49">
+      <c r="E29" s="48">
         <v>3450092096</v>
       </c>
       <c r="F29" s="12" t="s">
@@ -1964,10 +2100,10 @@
       <c r="G29" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H29" s="52" t="s">
+      <c r="H29" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="I29" s="51">
+      <c r="I29" s="50">
         <v>45926</v>
       </c>
     </row>
@@ -1978,13 +2114,13 @@
       <c r="B30" s="7">
         <v>45926</v>
       </c>
-      <c r="C30" s="27">
+      <c r="C30" s="26">
         <v>45936</v>
       </c>
-      <c r="D30" s="24">
+      <c r="D30" s="23">
         <v>134658593</v>
       </c>
-      <c r="E30" s="49">
+      <c r="E30" s="48">
         <v>3450092118</v>
       </c>
       <c r="F30" s="12" t="s">
@@ -1993,10 +2129,10 @@
       <c r="G30" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H30" s="52" t="s">
+      <c r="H30" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="I30" s="51">
+      <c r="I30" s="50">
         <v>45926</v>
       </c>
     </row>
@@ -2007,13 +2143,13 @@
       <c r="B31" s="7">
         <v>45926</v>
       </c>
-      <c r="C31" s="27">
+      <c r="C31" s="26">
         <v>45936</v>
       </c>
-      <c r="D31" s="24">
+      <c r="D31" s="23">
         <v>134662051</v>
       </c>
-      <c r="E31" s="49">
+      <c r="E31" s="48">
         <v>3450092360</v>
       </c>
       <c r="F31" s="12" t="s">
@@ -2022,10 +2158,10 @@
       <c r="G31" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H31" s="52" t="s">
+      <c r="H31" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="I31" s="51">
+      <c r="I31" s="50">
         <v>45926</v>
       </c>
     </row>
@@ -2036,13 +2172,13 @@
       <c r="B32" s="7">
         <v>45926</v>
       </c>
-      <c r="C32" s="27">
+      <c r="C32" s="26">
         <v>45936</v>
       </c>
-      <c r="D32" s="24">
+      <c r="D32" s="23">
         <v>134665397</v>
       </c>
-      <c r="E32" s="49">
+      <c r="E32" s="48">
         <v>3450092536</v>
       </c>
       <c r="F32" s="12" t="s">
@@ -2051,10 +2187,10 @@
       <c r="G32" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H32" s="52" t="s">
+      <c r="H32" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="I32" s="51">
+      <c r="I32" s="50">
         <v>45926</v>
       </c>
     </row>
@@ -2065,13 +2201,13 @@
       <c r="B33" s="7">
         <v>45926</v>
       </c>
-      <c r="C33" s="27">
+      <c r="C33" s="26">
         <v>45936</v>
       </c>
-      <c r="D33" s="24">
+      <c r="D33" s="23">
         <v>134668994</v>
       </c>
-      <c r="E33" s="49">
+      <c r="E33" s="48">
         <v>3450092833</v>
       </c>
       <c r="F33" s="12" t="s">
@@ -2080,10 +2216,10 @@
       <c r="G33" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H33" s="52" t="s">
+      <c r="H33" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="I33" s="51">
+      <c r="I33" s="50">
         <v>45926</v>
       </c>
     </row>
@@ -2094,13 +2230,13 @@
       <c r="B34" s="7">
         <v>45926</v>
       </c>
-      <c r="C34" s="27">
+      <c r="C34" s="26">
         <v>45936</v>
       </c>
-      <c r="D34" s="24">
+      <c r="D34" s="23">
         <v>134669432</v>
       </c>
-      <c r="E34" s="49">
+      <c r="E34" s="48">
         <v>3450092899</v>
       </c>
       <c r="F34" s="12" t="s">
@@ -2109,10 +2245,10 @@
       <c r="G34" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H34" s="52" t="s">
+      <c r="H34" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="I34" s="51">
+      <c r="I34" s="50">
         <v>45926</v>
       </c>
     </row>
@@ -2120,85 +2256,85 @@
       <c r="A35" s="6"/>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
-      <c r="D35" s="46"/>
+      <c r="D35" s="45"/>
       <c r="E35" s="18"/>
-      <c r="F35" s="50"/>
+      <c r="F35" s="49"/>
       <c r="G35" s="20"/>
       <c r="H35" s="9"/>
-      <c r="I35" s="26"/>
+      <c r="I35" s="25"/>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="6"/>
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
-      <c r="D36" s="24"/>
+      <c r="D36" s="23"/>
       <c r="E36" s="18"/>
       <c r="F36" s="19"/>
       <c r="G36" s="20"/>
       <c r="H36" s="9"/>
-      <c r="I36" s="26"/>
+      <c r="I36" s="25"/>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="6"/>
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
-      <c r="D37" s="24"/>
+      <c r="D37" s="23"/>
       <c r="E37" s="18"/>
       <c r="F37" s="19"/>
       <c r="G37" s="20"/>
       <c r="H37" s="9"/>
-      <c r="I37" s="26"/>
+      <c r="I37" s="25"/>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" s="6"/>
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
-      <c r="D38" s="24"/>
+      <c r="D38" s="23"/>
       <c r="E38" s="18"/>
       <c r="F38" s="12"/>
-      <c r="G38" s="23"/>
+      <c r="G38" s="22"/>
       <c r="H38" s="9"/>
-      <c r="I38" s="26"/>
+      <c r="I38" s="25"/>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" s="6"/>
       <c r="B39" s="7"/>
       <c r="C39" s="7"/>
-      <c r="D39" s="24"/>
+      <c r="D39" s="23"/>
       <c r="E39" s="18"/>
       <c r="F39" s="12"/>
-      <c r="G39" s="23"/>
+      <c r="G39" s="22"/>
       <c r="H39" s="9"/>
-      <c r="I39" s="26"/>
+      <c r="I39" s="25"/>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" s="6"/>
       <c r="B40" s="7"/>
       <c r="C40" s="7"/>
-      <c r="D40" s="24"/>
+      <c r="D40" s="23"/>
       <c r="E40" s="18"/>
       <c r="F40" s="19"/>
       <c r="G40" s="20"/>
       <c r="H40" s="9"/>
-      <c r="I40" s="26"/>
+      <c r="I40" s="25"/>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" s="6"/>
       <c r="B41" s="7"/>
       <c r="C41" s="7"/>
-      <c r="D41" s="24"/>
+      <c r="D41" s="23"/>
       <c r="E41" s="18"/>
       <c r="F41" s="19"/>
       <c r="G41" s="20"/>
       <c r="H41" s="9"/>
-      <c r="I41" s="26"/>
+      <c r="I41" s="25"/>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" s="6"/>
       <c r="B42" s="7"/>
       <c r="C42" s="7"/>
-      <c r="D42" s="22"/>
-      <c r="E42" s="22"/>
+      <c r="D42" s="21"/>
+      <c r="E42" s="21"/>
       <c r="F42" s="15"/>
       <c r="G42" s="6"/>
       <c r="H42" s="9"/>
@@ -2413,10 +2549,10 @@
       <c r="B2" s="7">
         <v>45929</v>
       </c>
-      <c r="C2" s="27">
+      <c r="C2" s="26">
         <v>45937</v>
       </c>
-      <c r="D2" s="24" t="s">
+      <c r="D2" s="23" t="s">
         <v>61</v>
       </c>
       <c r="E2" s="18">
@@ -2428,10 +2564,10 @@
       <c r="G2" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="H2" s="54" t="s">
+      <c r="H2" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="I2" s="51"/>
+      <c r="I2" s="50"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
@@ -2440,25 +2576,25 @@
       <c r="B3" s="7">
         <v>45934</v>
       </c>
-      <c r="C3" s="27">
+      <c r="C3" s="26">
         <v>45937</v>
       </c>
-      <c r="D3" s="47" t="s">
+      <c r="D3" s="46" t="s">
         <v>61</v>
       </c>
       <c r="E3" s="18">
         <v>3450099444</v>
       </c>
-      <c r="F3" s="30" t="s">
+      <c r="F3" s="29" t="s">
         <v>65</v>
       </c>
       <c r="G3" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="H3" s="52" t="s">
+      <c r="H3" s="51" t="s">
         <v>66</v>
       </c>
-      <c r="I3" s="51"/>
+      <c r="I3" s="50"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
@@ -2467,10 +2603,10 @@
       <c r="B4" s="7">
         <v>45929</v>
       </c>
-      <c r="C4" s="27">
+      <c r="C4" s="26">
         <v>45937</v>
       </c>
-      <c r="D4" s="24">
+      <c r="D4" s="23">
         <v>134681507</v>
       </c>
       <c r="E4" s="18">
@@ -2482,10 +2618,10 @@
       <c r="G4" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="52" t="s">
+      <c r="H4" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="61">
+      <c r="I4" s="59">
         <v>45929</v>
       </c>
     </row>
@@ -2496,10 +2632,10 @@
       <c r="B5" s="7">
         <v>45929</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="26">
         <v>45937</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="23">
         <v>134683357</v>
       </c>
       <c r="E5" s="18">
@@ -2511,10 +2647,10 @@
       <c r="G5" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="53" t="s">
+      <c r="H5" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="I5" s="51">
+      <c r="I5" s="50">
         <v>45929</v>
       </c>
     </row>
@@ -2525,10 +2661,10 @@
       <c r="B6" s="7">
         <v>45929</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="26">
         <v>45937</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="23">
         <v>134689189</v>
       </c>
       <c r="E6" s="18">
@@ -2537,13 +2673,13 @@
       <c r="F6" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="G6" s="25" t="s">
+      <c r="G6" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="57" t="s">
+      <c r="H6" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="I6" s="51">
+      <c r="I6" s="50">
         <v>45929</v>
       </c>
     </row>
@@ -2554,10 +2690,10 @@
       <c r="B7" s="7">
         <v>45929</v>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="26">
         <v>45937</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="23">
         <v>134691356</v>
       </c>
       <c r="E7" s="18">
@@ -2566,13 +2702,13 @@
       <c r="F7" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="G7" s="25" t="s">
+      <c r="G7" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="H7" s="54" t="s">
+      <c r="H7" s="53" t="s">
         <v>18</v>
       </c>
-      <c r="I7" s="51">
+      <c r="I7" s="50">
         <v>45929</v>
       </c>
     </row>
@@ -2583,10 +2719,10 @@
       <c r="B8" s="7">
         <v>45929</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="26">
         <v>45937</v>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="23">
         <v>134691773</v>
       </c>
       <c r="E8" s="18">
@@ -2598,10 +2734,10 @@
       <c r="G8" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H8" s="55" t="s">
+      <c r="H8" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="I8" s="51">
+      <c r="I8" s="50">
         <v>45929</v>
       </c>
     </row>
@@ -2612,10 +2748,10 @@
       <c r="B9" s="7">
         <v>45929</v>
       </c>
-      <c r="C9" s="27">
+      <c r="C9" s="26">
         <v>45937</v>
       </c>
-      <c r="D9" s="24">
+      <c r="D9" s="23">
         <v>134680144</v>
       </c>
       <c r="E9" s="18">
@@ -2627,10 +2763,10 @@
       <c r="G9" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="H9" s="55" t="s">
+      <c r="H9" s="54" t="s">
         <v>73</v>
       </c>
-      <c r="I9" s="58">
+      <c r="I9" s="57">
         <v>45936</v>
       </c>
     </row>
@@ -2641,10 +2777,10 @@
       <c r="B10" s="7">
         <v>45930</v>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="26">
         <v>45937</v>
       </c>
-      <c r="D10" s="24">
+      <c r="D10" s="23">
         <v>134711738</v>
       </c>
       <c r="E10" s="18">
@@ -2656,10 +2792,10 @@
       <c r="G10" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="H10" s="52" t="s">
+      <c r="H10" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="I10" s="51">
+      <c r="I10" s="50">
         <v>45930</v>
       </c>
     </row>
@@ -2670,10 +2806,10 @@
       <c r="B11" s="7">
         <v>45931</v>
       </c>
-      <c r="C11" s="27">
+      <c r="C11" s="26">
         <v>45937</v>
       </c>
-      <c r="D11" s="24">
+      <c r="D11" s="23">
         <v>134720385</v>
       </c>
       <c r="E11" s="18">
@@ -2685,10 +2821,10 @@
       <c r="G11" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="H11" s="52" t="s">
+      <c r="H11" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="I11" s="51">
+      <c r="I11" s="50">
         <v>45931</v>
       </c>
     </row>
@@ -2699,10 +2835,10 @@
       <c r="B12" s="7">
         <v>45949</v>
       </c>
-      <c r="C12" s="27">
+      <c r="C12" s="26">
         <v>45937</v>
       </c>
-      <c r="D12" s="24">
+      <c r="D12" s="23">
         <v>134755230</v>
       </c>
       <c r="E12" s="18">
@@ -2714,10 +2850,10 @@
       <c r="G12" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="H12" s="60" t="s">
+      <c r="H12" s="51" t="s">
         <v>78</v>
       </c>
-      <c r="I12" s="51">
+      <c r="I12" s="50">
         <v>45937</v>
       </c>
     </row>
@@ -2728,10 +2864,10 @@
       <c r="B13" s="7">
         <v>45933</v>
       </c>
-      <c r="C13" s="27">
+      <c r="C13" s="26">
         <v>45937</v>
       </c>
-      <c r="D13" s="24">
+      <c r="D13" s="23">
         <v>134775095</v>
       </c>
       <c r="E13" s="18">
@@ -2743,10 +2879,10 @@
       <c r="G13" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="H13" s="60" t="s">
+      <c r="H13" s="51" t="s">
         <v>73</v>
       </c>
-      <c r="I13" s="51">
+      <c r="I13" s="50">
         <v>45936</v>
       </c>
     </row>
@@ -2757,10 +2893,10 @@
       <c r="B14" s="7">
         <v>45933</v>
       </c>
-      <c r="C14" s="27">
+      <c r="C14" s="26">
         <v>45937</v>
       </c>
-      <c r="D14" s="24">
+      <c r="D14" s="23">
         <v>134772972</v>
       </c>
       <c r="E14" s="18">
@@ -2772,10 +2908,10 @@
       <c r="G14" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="H14" s="52" t="s">
+      <c r="H14" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="I14" s="51">
+      <c r="I14" s="50">
         <v>45933</v>
       </c>
     </row>
@@ -2786,10 +2922,10 @@
       <c r="B15" s="7">
         <v>45933</v>
       </c>
-      <c r="C15" s="27">
+      <c r="C15" s="26">
         <v>45937</v>
       </c>
-      <c r="D15" s="24">
+      <c r="D15" s="23">
         <v>134770331</v>
       </c>
       <c r="E15" s="18">
@@ -2801,10 +2937,10 @@
       <c r="G15" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="H15" s="52" t="s">
+      <c r="H15" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="I15" s="51">
+      <c r="I15" s="50">
         <v>45933</v>
       </c>
     </row>
@@ -2815,10 +2951,10 @@
       <c r="B16" s="7">
         <v>45932</v>
       </c>
-      <c r="C16" s="27">
+      <c r="C16" s="26">
         <v>45937</v>
       </c>
-      <c r="D16" s="24">
+      <c r="D16" s="23">
         <v>134757544</v>
       </c>
       <c r="E16" s="18">
@@ -2830,10 +2966,10 @@
       <c r="G16" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="H16" s="52" t="s">
+      <c r="H16" s="51" t="s">
         <v>73</v>
       </c>
-      <c r="I16" s="51">
+      <c r="I16" s="50">
         <v>45936</v>
       </c>
     </row>
@@ -2844,10 +2980,10 @@
       <c r="B17" s="7">
         <v>45931</v>
       </c>
-      <c r="C17" s="27">
+      <c r="C17" s="26">
         <v>45937</v>
       </c>
-      <c r="D17" s="24">
+      <c r="D17" s="23">
         <v>134623063</v>
       </c>
       <c r="E17" s="18">
@@ -2859,10 +2995,10 @@
       <c r="G17" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="H17" s="60" t="s">
+      <c r="H17" s="51" t="s">
         <v>83</v>
       </c>
-      <c r="I17" s="51">
+      <c r="I17" s="50">
         <v>45926</v>
       </c>
     </row>
@@ -2873,10 +3009,10 @@
       <c r="B18" s="7">
         <v>45926</v>
       </c>
-      <c r="C18" s="27">
+      <c r="C18" s="26">
         <v>45937</v>
       </c>
-      <c r="D18" s="24">
+      <c r="D18" s="23">
         <v>134680848</v>
       </c>
       <c r="E18" s="18">
@@ -2888,10 +3024,10 @@
       <c r="G18" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H18" s="52" t="s">
+      <c r="H18" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="I18" s="51">
+      <c r="I18" s="50">
         <v>45926</v>
       </c>
     </row>
@@ -2902,10 +3038,10 @@
       <c r="B19" s="7">
         <v>45929</v>
       </c>
-      <c r="C19" s="27">
+      <c r="C19" s="26">
         <v>45937</v>
       </c>
-      <c r="D19" s="24">
+      <c r="D19" s="23">
         <v>134681098</v>
       </c>
       <c r="E19" s="18">
@@ -2917,10 +3053,10 @@
       <c r="G19" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H19" s="52" t="s">
+      <c r="H19" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="I19" s="51">
+      <c r="I19" s="50">
         <v>45929</v>
       </c>
     </row>
@@ -2931,10 +3067,10 @@
       <c r="B20" s="7">
         <v>45929</v>
       </c>
-      <c r="C20" s="27">
+      <c r="C20" s="26">
         <v>45937</v>
       </c>
-      <c r="D20" s="24">
+      <c r="D20" s="23">
         <v>134683463</v>
       </c>
       <c r="E20" s="18">
@@ -2946,10 +3082,10 @@
       <c r="G20" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H20" s="52" t="s">
+      <c r="H20" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="I20" s="58">
+      <c r="I20" s="57">
         <v>45929</v>
       </c>
     </row>
@@ -2960,10 +3096,10 @@
       <c r="B21" s="7">
         <v>45929</v>
       </c>
-      <c r="C21" s="27">
+      <c r="C21" s="26">
         <v>45937</v>
       </c>
-      <c r="D21" s="24">
+      <c r="D21" s="23">
         <v>134684719</v>
       </c>
       <c r="E21" s="18">
@@ -2975,10 +3111,10 @@
       <c r="G21" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H21" s="52" t="s">
+      <c r="H21" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="I21" s="51">
+      <c r="I21" s="50">
         <v>45929</v>
       </c>
     </row>
@@ -2989,10 +3125,10 @@
       <c r="B22" s="7">
         <v>45929</v>
       </c>
-      <c r="C22" s="27">
+      <c r="C22" s="26">
         <v>45937</v>
       </c>
-      <c r="D22" s="24">
+      <c r="D22" s="23">
         <v>134679649</v>
       </c>
       <c r="E22" s="18">
@@ -3004,10 +3140,10 @@
       <c r="G22" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="H22" s="52" t="s">
+      <c r="H22" s="51" t="s">
         <v>39</v>
       </c>
-      <c r="I22" s="51">
+      <c r="I22" s="50">
         <v>45936</v>
       </c>
     </row>
@@ -3018,10 +3154,10 @@
       <c r="B23" s="7">
         <v>45929</v>
       </c>
-      <c r="C23" s="27">
+      <c r="C23" s="26">
         <v>45937</v>
       </c>
-      <c r="D23" s="24">
+      <c r="D23" s="23">
         <v>134687908</v>
       </c>
       <c r="E23" s="18">
@@ -3033,10 +3169,10 @@
       <c r="G23" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H23" s="52" t="s">
+      <c r="H23" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="I23" s="51">
+      <c r="I23" s="50">
         <v>45929</v>
       </c>
     </row>
@@ -3047,10 +3183,10 @@
       <c r="B24" s="7">
         <v>45929</v>
       </c>
-      <c r="C24" s="27">
+      <c r="C24" s="26">
         <v>45937</v>
       </c>
-      <c r="D24" s="24">
+      <c r="D24" s="23">
         <v>134688236</v>
       </c>
       <c r="E24" s="18">
@@ -3062,10 +3198,10 @@
       <c r="G24" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H24" s="52" t="s">
+      <c r="H24" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="I24" s="51">
+      <c r="I24" s="50">
         <v>45929</v>
       </c>
     </row>
@@ -3076,10 +3212,10 @@
       <c r="B25" s="7">
         <v>45929</v>
       </c>
-      <c r="C25" s="27">
+      <c r="C25" s="26">
         <v>45937</v>
       </c>
-      <c r="D25" s="24">
+      <c r="D25" s="23">
         <v>134688982</v>
       </c>
       <c r="E25" s="18">
@@ -3091,10 +3227,10 @@
       <c r="G25" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H25" s="59" t="s">
+      <c r="H25" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="I25" s="51">
+      <c r="I25" s="50">
         <v>45929</v>
       </c>
     </row>
@@ -3105,10 +3241,10 @@
       <c r="B26" s="7">
         <v>45929</v>
       </c>
-      <c r="C26" s="27">
+      <c r="C26" s="26">
         <v>45937</v>
       </c>
-      <c r="D26" s="24">
+      <c r="D26" s="23">
         <v>134689719</v>
       </c>
       <c r="E26" s="18">
@@ -3120,10 +3256,10 @@
       <c r="G26" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H26" s="52" t="s">
+      <c r="H26" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="I26" s="51">
+      <c r="I26" s="50">
         <v>45929</v>
       </c>
     </row>
@@ -3134,10 +3270,10 @@
       <c r="B27" s="7">
         <v>45929</v>
       </c>
-      <c r="C27" s="27">
+      <c r="C27" s="26">
         <v>45937</v>
       </c>
-      <c r="D27" s="24">
+      <c r="D27" s="23">
         <v>134689748</v>
       </c>
       <c r="E27" s="18">
@@ -3149,10 +3285,10 @@
       <c r="G27" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H27" s="52" t="s">
+      <c r="H27" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="I27" s="51">
+      <c r="I27" s="50">
         <v>45929</v>
       </c>
     </row>
@@ -3163,10 +3299,10 @@
       <c r="B28" s="7">
         <v>45929</v>
       </c>
-      <c r="C28" s="27">
+      <c r="C28" s="26">
         <v>45937</v>
       </c>
-      <c r="D28" s="24">
+      <c r="D28" s="23">
         <v>134692186</v>
       </c>
       <c r="E28" s="18">
@@ -3178,10 +3314,10 @@
       <c r="G28" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H28" s="52" t="s">
+      <c r="H28" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="I28" s="51">
+      <c r="I28" s="50">
         <v>45929</v>
       </c>
     </row>
@@ -3192,10 +3328,10 @@
       <c r="B29" s="7">
         <v>45929</v>
       </c>
-      <c r="C29" s="27">
+      <c r="C29" s="26">
         <v>45937</v>
       </c>
-      <c r="D29" s="24">
+      <c r="D29" s="23">
         <v>134694208</v>
       </c>
       <c r="E29" s="18">
@@ -3207,10 +3343,10 @@
       <c r="G29" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H29" s="52" t="s">
+      <c r="H29" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="I29" s="51">
+      <c r="I29" s="50">
         <v>45929</v>
       </c>
     </row>
@@ -3221,10 +3357,10 @@
       <c r="B30" s="7">
         <v>45953</v>
       </c>
-      <c r="C30" s="27">
+      <c r="C30" s="26">
         <v>45937</v>
       </c>
-      <c r="D30" s="24">
+      <c r="D30" s="23">
         <v>134621154</v>
       </c>
       <c r="E30" s="18">
@@ -3236,45 +3372,45 @@
       <c r="G30" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="H30" s="60" t="s">
+      <c r="H30" s="51" t="s">
         <v>97</v>
       </c>
-      <c r="I30" s="51">
+      <c r="I30" s="50">
         <v>45926</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="6"/>
       <c r="B31" s="7"/>
-      <c r="C31" s="27"/>
-      <c r="D31" s="46"/>
-      <c r="E31" s="56"/>
-      <c r="F31" s="35"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="45"/>
+      <c r="E31" s="55"/>
+      <c r="F31" s="34"/>
       <c r="G31" s="20"/>
-      <c r="H31" s="31"/>
-      <c r="I31" s="26"/>
+      <c r="H31" s="30"/>
+      <c r="I31" s="25"/>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="6"/>
       <c r="B32" s="7"/>
-      <c r="C32" s="27"/>
-      <c r="D32" s="24"/>
+      <c r="C32" s="26"/>
+      <c r="D32" s="23"/>
       <c r="E32" s="18"/>
       <c r="F32" s="12"/>
       <c r="G32" s="20"/>
       <c r="H32" s="9"/>
-      <c r="I32" s="26"/>
+      <c r="I32" s="25"/>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="6"/>
       <c r="B33" s="8"/>
       <c r="C33" s="7"/>
-      <c r="D33" s="22"/>
-      <c r="E33" s="22"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
       <c r="F33" s="15"/>
       <c r="G33" s="6"/>
       <c r="H33" s="9"/>
-      <c r="I33" s="26"/>
+      <c r="I33" s="25"/>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="6"/>
@@ -3285,7 +3421,7 @@
       <c r="F34" s="9"/>
       <c r="G34" s="6"/>
       <c r="H34" s="9"/>
-      <c r="I34" s="26"/>
+      <c r="I34" s="25"/>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="6"/>
@@ -3296,7 +3432,7 @@
       <c r="F35" s="9"/>
       <c r="G35" s="6"/>
       <c r="H35" s="9"/>
-      <c r="I35" s="26"/>
+      <c r="I35" s="25"/>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="6"/>
@@ -3527,17 +3663,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BD26F43-5C8A-4C67-93F6-3B4E17ED8491}">
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="15.85546875" style="17" customWidth="1"/>
     <col min="3" max="3" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.5703125" style="17" customWidth="1"/>
     <col min="5" max="5" width="17.85546875" style="17" customWidth="1"/>
-    <col min="6" max="6" width="27" customWidth="1"/>
+    <col min="6" max="6" width="38" customWidth="1"/>
     <col min="7" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="31.5703125" customWidth="1"/>
-    <col min="9" max="9" width="21" style="26" customWidth="1"/>
+    <col min="9" max="9" width="21" style="25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -3565,7 +3701,7 @@
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="32" t="s">
+      <c r="I1" s="31" t="s">
         <v>8</v>
       </c>
     </row>
@@ -3573,389 +3709,720 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="21"/>
+      <c r="B2" s="61">
+        <v>45935</v>
+      </c>
+      <c r="C2" s="26">
+        <v>45938</v>
+      </c>
+      <c r="D2" s="23">
+        <v>134646233</v>
+      </c>
+      <c r="E2" s="18">
+        <v>3450091403</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="G2" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="62" t="s">
+        <v>99</v>
+      </c>
+      <c r="I2" s="63">
+        <v>45929</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="12"/>
+      <c r="B3" s="61">
+        <v>45948</v>
+      </c>
+      <c r="C3" s="26">
+        <v>45938</v>
+      </c>
+      <c r="D3" s="23">
+        <v>134693268</v>
+      </c>
+      <c r="E3" s="18">
+        <v>3450094230</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="G3" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="H3" s="62" t="s">
+        <v>101</v>
+      </c>
+      <c r="I3" s="63">
+        <v>45937</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="12"/>
+      <c r="B4" s="61">
+        <v>45930</v>
+      </c>
+      <c r="C4" s="26">
+        <v>45938</v>
+      </c>
+      <c r="D4" s="23">
+        <v>134715792</v>
+      </c>
+      <c r="E4" s="18">
+        <v>3450095891</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="G4" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" s="62" t="s">
+        <v>103</v>
+      </c>
+      <c r="I4" s="63">
+        <v>45930</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="15"/>
+      <c r="B5" s="61">
+        <v>45930</v>
+      </c>
+      <c r="C5" s="26">
+        <v>45938</v>
+      </c>
+      <c r="D5" s="23">
+        <v>134716555</v>
+      </c>
+      <c r="E5" s="18">
+        <v>3450095980</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="G5" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" s="62" t="s">
+        <v>105</v>
+      </c>
+      <c r="I5" s="63">
+        <v>45930</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="28"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="9"/>
+      <c r="B6" s="61">
+        <v>45931</v>
+      </c>
+      <c r="C6" s="26">
+        <v>45938</v>
+      </c>
+      <c r="D6" s="23">
+        <v>134723358</v>
+      </c>
+      <c r="E6" s="18">
+        <v>3450096232</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="G6" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="62" t="s">
+        <v>107</v>
+      </c>
+      <c r="I6" s="63">
+        <v>45931</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="20"/>
-      <c r="H7" s="9"/>
+      <c r="B7" s="61">
+        <v>45956</v>
+      </c>
+      <c r="C7" s="26">
+        <v>45938</v>
+      </c>
+      <c r="D7" s="23">
+        <v>134707736</v>
+      </c>
+      <c r="E7" s="18">
+        <v>3450093780</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" s="62" t="s">
+        <v>109</v>
+      </c>
+      <c r="I7" s="50">
+        <v>45956</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="9"/>
+      <c r="B8" s="61">
+        <v>45932</v>
+      </c>
+      <c r="C8" s="26">
+        <v>45938</v>
+      </c>
+      <c r="D8" s="23">
+        <v>134757273</v>
+      </c>
+      <c r="E8" s="18">
+        <v>3450098290</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="G8" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="51" t="s">
+        <v>20</v>
+      </c>
+      <c r="I8" s="50">
+        <v>45932</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="9"/>
+      <c r="B9" s="61">
+        <v>45933</v>
+      </c>
+      <c r="C9" s="26">
+        <v>45938</v>
+      </c>
+      <c r="D9" s="23">
+        <v>134783975</v>
+      </c>
+      <c r="E9" s="18">
+        <v>3450099587</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9" s="51" t="s">
+        <v>107</v>
+      </c>
+      <c r="I9" s="50">
+        <v>45933</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="23"/>
-      <c r="H10" s="9"/>
+      <c r="B10" s="61">
+        <v>45936</v>
+      </c>
+      <c r="C10" s="26">
+        <v>45938</v>
+      </c>
+      <c r="D10" s="23">
+        <v>134806114</v>
+      </c>
+      <c r="E10" s="18">
+        <v>3450100346</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="G10" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" s="51" t="s">
+        <v>113</v>
+      </c>
+      <c r="I10" s="50">
+        <v>45936</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="28"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="9"/>
+      <c r="B11" s="61">
+        <v>45925</v>
+      </c>
+      <c r="C11" s="26">
+        <v>45938</v>
+      </c>
+      <c r="D11" s="23">
+        <v>134633677</v>
+      </c>
+      <c r="E11" s="18">
+        <v>3450090589</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="H11" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="I11" s="50">
+        <v>45930</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="23"/>
-      <c r="H12" s="9"/>
+      <c r="B12" s="61">
+        <v>45940</v>
+      </c>
+      <c r="C12" s="26">
+        <v>45938</v>
+      </c>
+      <c r="D12" s="23">
+        <v>134633366</v>
+      </c>
+      <c r="E12" s="18">
+        <v>3450084715</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="G12" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="H12" s="51" t="s">
+        <v>117</v>
+      </c>
+      <c r="I12" s="50">
+        <v>45930</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="9"/>
+      <c r="B13" s="61">
+        <v>45930</v>
+      </c>
+      <c r="C13" s="26">
+        <v>45938</v>
+      </c>
+      <c r="D13" s="23">
+        <v>134701456</v>
+      </c>
+      <c r="E13" s="18">
+        <v>3450094703</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" s="51" t="s">
+        <v>20</v>
+      </c>
+      <c r="I13" s="50">
+        <v>45930</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="9"/>
+      <c r="B14" s="61">
+        <v>45929</v>
+      </c>
+      <c r="C14" s="26">
+        <v>45938</v>
+      </c>
+      <c r="D14" s="23">
+        <v>134707976</v>
+      </c>
+      <c r="E14" s="18">
+        <v>3450093746</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="G14" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H14" s="51" t="s">
+        <v>120</v>
+      </c>
+      <c r="I14" s="50">
+        <v>45929</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="9"/>
+      <c r="B15" s="7">
+        <v>45925</v>
+      </c>
+      <c r="C15" s="26">
+        <v>45938</v>
+      </c>
+      <c r="D15" s="23">
+        <v>134640712</v>
+      </c>
+      <c r="E15" s="18">
+        <v>3450090996</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="G15" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H15" s="51" t="s">
+        <v>122</v>
+      </c>
+      <c r="I15" s="50">
+        <v>45925</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="6"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="9"/>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="6"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="9"/>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="6"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="27"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="23"/>
-      <c r="H18" s="9"/>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="6"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="9"/>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="6"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="27"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="9"/>
-    </row>
-    <row r="21" spans="1:8">
+      <c r="B16" s="7">
+        <v>45930</v>
+      </c>
+      <c r="C16" s="26">
+        <v>45938</v>
+      </c>
+      <c r="D16" s="23">
+        <v>134713489</v>
+      </c>
+      <c r="E16" s="18">
+        <v>3450095616</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="G16" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="H16" s="51" t="s">
+        <v>124</v>
+      </c>
+      <c r="I16" s="50">
+        <v>45930</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="7">
+        <v>45930</v>
+      </c>
+      <c r="C17" s="26">
+        <v>45938</v>
+      </c>
+      <c r="D17" s="23">
+        <v>134716459</v>
+      </c>
+      <c r="E17" s="18">
+        <v>3450095968</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="G17" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H17" s="51" t="s">
+        <v>126</v>
+      </c>
+      <c r="I17" s="50">
+        <v>45930</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="7">
+        <v>45930</v>
+      </c>
+      <c r="C18" s="26">
+        <v>45938</v>
+      </c>
+      <c r="D18" s="23">
+        <v>134705705</v>
+      </c>
+      <c r="E18" s="18">
+        <v>3450095033</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="G18" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="I18" s="50">
+        <v>45930</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="7">
+        <v>45948</v>
+      </c>
+      <c r="C19" s="26">
+        <v>45938</v>
+      </c>
+      <c r="D19" s="23">
+        <v>134800087</v>
+      </c>
+      <c r="E19" s="18">
+        <v>3450100060</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="G19" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="H19" s="51" t="s">
+        <v>101</v>
+      </c>
+      <c r="I19" s="50">
+        <v>45937</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="7">
+        <v>45930</v>
+      </c>
+      <c r="C20" s="26">
+        <v>45938</v>
+      </c>
+      <c r="D20" s="23">
+        <v>134700416</v>
+      </c>
+      <c r="E20" s="18">
+        <v>3450094648</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="H20" s="51" t="s">
+        <v>39</v>
+      </c>
+      <c r="I20" s="50">
+        <v>45937</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" s="6"/>
       <c r="B21" s="7"/>
-      <c r="C21" s="27"/>
-      <c r="D21" s="28"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="12"/>
+      <c r="C21" s="26"/>
+      <c r="D21" s="60"/>
+      <c r="E21" s="55"/>
+      <c r="F21" s="34"/>
       <c r="G21" s="20"/>
       <c r="H21" s="9"/>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:9">
       <c r="A22" s="6"/>
       <c r="B22" s="7"/>
-      <c r="C22" s="27"/>
-      <c r="D22" s="28"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="23"/>
       <c r="E22" s="18"/>
       <c r="F22" s="12"/>
-      <c r="G22" s="20"/>
+      <c r="G22" s="22"/>
       <c r="H22" s="9"/>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:9">
       <c r="A23" s="6"/>
       <c r="B23" s="7"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="28"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="27"/>
       <c r="E23" s="18"/>
       <c r="F23" s="12"/>
       <c r="G23" s="20"/>
       <c r="H23" s="9"/>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:9">
       <c r="A24" s="6"/>
       <c r="B24" s="7"/>
-      <c r="C24" s="27"/>
-      <c r="D24" s="24"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="27"/>
       <c r="E24" s="18"/>
       <c r="F24" s="12"/>
-      <c r="G24" s="23"/>
+      <c r="G24" s="20"/>
       <c r="H24" s="9"/>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:9">
       <c r="A25" s="6"/>
       <c r="B25" s="7"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="28"/>
+      <c r="C25" s="26"/>
+      <c r="D25" s="27"/>
       <c r="E25" s="18"/>
       <c r="F25" s="12"/>
       <c r="G25" s="20"/>
       <c r="H25" s="9"/>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:9">
       <c r="A26" s="6"/>
       <c r="B26" s="7"/>
-      <c r="C26" s="27"/>
-      <c r="D26" s="28"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="27"/>
       <c r="E26" s="18"/>
       <c r="F26" s="12"/>
       <c r="G26" s="20"/>
       <c r="H26" s="9"/>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:9">
       <c r="A27" s="6"/>
       <c r="B27" s="7"/>
-      <c r="C27" s="27"/>
-      <c r="D27" s="28"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="23"/>
       <c r="E27" s="18"/>
       <c r="F27" s="12"/>
-      <c r="G27" s="20"/>
+      <c r="G27" s="22"/>
       <c r="H27" s="9"/>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:9">
       <c r="A28" s="6"/>
       <c r="B28" s="7"/>
-      <c r="C28" s="27"/>
-      <c r="D28" s="28"/>
+      <c r="C28" s="26"/>
+      <c r="D28" s="23"/>
       <c r="E28" s="18"/>
       <c r="F28" s="12"/>
-      <c r="G28" s="20"/>
+      <c r="G28" s="22"/>
       <c r="H28" s="9"/>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:9">
       <c r="A29" s="6"/>
       <c r="B29" s="7"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="24"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="23"/>
       <c r="E29" s="18"/>
       <c r="F29" s="12"/>
-      <c r="G29" s="23"/>
+      <c r="G29" s="22"/>
       <c r="H29" s="9"/>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:9">
       <c r="A30" s="6"/>
       <c r="B30" s="7"/>
-      <c r="C30" s="27"/>
-      <c r="D30" s="24"/>
+      <c r="C30" s="26"/>
+      <c r="D30" s="23"/>
       <c r="E30" s="18"/>
       <c r="F30" s="12"/>
-      <c r="G30" s="23"/>
+      <c r="G30" s="22"/>
       <c r="H30" s="9"/>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:9">
       <c r="A31" s="6"/>
       <c r="B31" s="7"/>
-      <c r="C31" s="27"/>
-      <c r="D31" s="24"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="23"/>
       <c r="E31" s="18"/>
       <c r="F31" s="12"/>
-      <c r="G31" s="23"/>
+      <c r="G31" s="22"/>
       <c r="H31" s="9"/>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:9">
       <c r="A32" s="6"/>
       <c r="B32" s="7"/>
-      <c r="C32" s="27"/>
-      <c r="D32" s="24"/>
+      <c r="C32" s="26"/>
+      <c r="D32" s="23"/>
       <c r="E32" s="18"/>
       <c r="F32" s="12"/>
-      <c r="G32" s="23"/>
+      <c r="G32" s="22"/>
       <c r="H32" s="9"/>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="6"/>
       <c r="B33" s="7"/>
-      <c r="C33" s="27"/>
-      <c r="D33" s="24"/>
+      <c r="C33" s="26"/>
+      <c r="D33" s="23"/>
       <c r="E33" s="18"/>
       <c r="F33" s="12"/>
-      <c r="G33" s="23"/>
+      <c r="G33" s="22"/>
       <c r="H33" s="9"/>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="6"/>
       <c r="B34" s="7"/>
-      <c r="C34" s="27"/>
-      <c r="D34" s="24"/>
+      <c r="C34" s="26"/>
+      <c r="D34" s="23"/>
       <c r="E34" s="18"/>
       <c r="F34" s="12"/>
-      <c r="G34" s="23"/>
+      <c r="G34" s="22"/>
       <c r="H34" s="9"/>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="6"/>
-      <c r="B35" s="7"/>
-      <c r="C35" s="27"/>
-      <c r="D35" s="24"/>
-      <c r="E35" s="18"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="23"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="6"/>
       <c r="H35" s="9"/>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="6"/>
-      <c r="B36" s="7"/>
-      <c r="C36" s="27"/>
-      <c r="D36" s="24"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="12"/>
-      <c r="G36" s="23"/>
+      <c r="B36" s="8"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="6"/>
       <c r="H36" s="9"/>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="6"/>
       <c r="B37" s="8"/>
       <c r="C37" s="7"/>
-      <c r="D37" s="22"/>
-      <c r="E37" s="22"/>
-      <c r="F37" s="15"/>
+      <c r="D37" s="8"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="9"/>
       <c r="G37" s="6"/>
       <c r="H37" s="9"/>
     </row>
@@ -3999,43 +4466,23 @@
       <c r="G41" s="6"/>
       <c r="H41" s="9"/>
     </row>
-    <row r="42" spans="1:8">
-      <c r="A42" s="6"/>
-      <c r="B42" s="8"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="9"/>
-    </row>
-    <row r="43" spans="1:8">
-      <c r="A43" s="6"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="9"/>
-    </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="2">
+    <cfRule type="notContainsBlanks" priority="3">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A17:A36" xr:uid="{F535CD1B-7EC8-4CD4-9DE2-4943F25AAD12}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A21:A34" xr:uid="{F535CD1B-7EC8-4CD4-9DE2-4943F25AAD12}">
       <formula1>#REF!</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G36" xr:uid="{9AF2051F-77D3-4586-8B0A-6A9380E3F6D6}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G34" xr:uid="{9AF2051F-77D3-4586-8B0A-6A9380E3F6D6}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A16" xr:uid="{E44F5A38-408F-4061-943F-128F4E144D8E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A20" xr:uid="{E44F5A38-408F-4061-943F-128F4E144D8E}">
       <formula1>$J$2</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B16" xr:uid="{20D23971-3A52-480D-B4EF-1652ABE6891E}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B14" xr:uid="{20D23971-3A52-480D-B4EF-1652ABE6891E}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4092,12 +4539,12 @@
       </c>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
-      <c r="D2" s="28"/>
+      <c r="D2" s="27"/>
       <c r="E2" s="8"/>
       <c r="F2" s="12"/>
-      <c r="G2" s="29"/>
+      <c r="G2" s="28"/>
       <c r="H2" s="9"/>
-      <c r="I2" s="26"/>
+      <c r="I2" s="25"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
@@ -4105,12 +4552,12 @@
       </c>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
-      <c r="D3" s="28"/>
+      <c r="D3" s="27"/>
       <c r="E3" s="8"/>
       <c r="F3" s="12"/>
-      <c r="G3" s="29"/>
+      <c r="G3" s="28"/>
       <c r="H3" s="9"/>
-      <c r="I3" s="26"/>
+      <c r="I3" s="25"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
@@ -4118,12 +4565,12 @@
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
-      <c r="D4" s="28"/>
+      <c r="D4" s="27"/>
       <c r="E4" s="8"/>
       <c r="F4" s="12"/>
-      <c r="G4" s="29"/>
+      <c r="G4" s="28"/>
       <c r="H4" s="9"/>
-      <c r="I4" s="26"/>
+      <c r="I4" s="25"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
@@ -4131,12 +4578,12 @@
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
-      <c r="D5" s="28"/>
+      <c r="D5" s="27"/>
       <c r="E5" s="8"/>
       <c r="F5" s="12"/>
-      <c r="G5" s="29"/>
+      <c r="G5" s="28"/>
       <c r="H5" s="9"/>
-      <c r="I5" s="26"/>
+      <c r="I5" s="25"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
@@ -4144,12 +4591,12 @@
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
-      <c r="D6" s="28"/>
+      <c r="D6" s="27"/>
       <c r="E6" s="8"/>
       <c r="F6" s="12"/>
-      <c r="G6" s="29"/>
+      <c r="G6" s="28"/>
       <c r="H6" s="9"/>
-      <c r="I6" s="26"/>
+      <c r="I6" s="25"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
@@ -4157,12 +4604,12 @@
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
-      <c r="D7" s="28"/>
+      <c r="D7" s="27"/>
       <c r="E7" s="8"/>
       <c r="F7" s="12"/>
-      <c r="G7" s="29"/>
+      <c r="G7" s="28"/>
       <c r="H7" s="9"/>
-      <c r="I7" s="26"/>
+      <c r="I7" s="25"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
@@ -4170,12 +4617,12 @@
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
-      <c r="D8" s="28"/>
+      <c r="D8" s="27"/>
       <c r="E8" s="8"/>
       <c r="F8" s="12"/>
-      <c r="G8" s="29"/>
+      <c r="G8" s="28"/>
       <c r="H8" s="9"/>
-      <c r="I8" s="26"/>
+      <c r="I8" s="25"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
@@ -4183,12 +4630,12 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
-      <c r="D9" s="28"/>
+      <c r="D9" s="27"/>
       <c r="E9" s="8"/>
       <c r="F9" s="12"/>
-      <c r="G9" s="29"/>
+      <c r="G9" s="28"/>
       <c r="H9" s="9"/>
-      <c r="I9" s="26"/>
+      <c r="I9" s="25"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
@@ -4196,12 +4643,12 @@
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
-      <c r="D10" s="28"/>
+      <c r="D10" s="27"/>
       <c r="E10" s="8"/>
       <c r="F10" s="12"/>
-      <c r="G10" s="29"/>
+      <c r="G10" s="28"/>
       <c r="H10" s="9"/>
-      <c r="I10" s="26"/>
+      <c r="I10" s="25"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
@@ -4209,12 +4656,12 @@
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
-      <c r="D11" s="28"/>
+      <c r="D11" s="27"/>
       <c r="E11" s="8"/>
       <c r="F11" s="12"/>
-      <c r="G11" s="29"/>
+      <c r="G11" s="28"/>
       <c r="H11" s="9"/>
-      <c r="I11" s="26"/>
+      <c r="I11" s="25"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
@@ -4222,12 +4669,12 @@
       </c>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
-      <c r="D12" s="28"/>
+      <c r="D12" s="27"/>
       <c r="E12" s="8"/>
       <c r="F12" s="12"/>
-      <c r="G12" s="29"/>
+      <c r="G12" s="28"/>
       <c r="H12" s="9"/>
-      <c r="I12" s="26"/>
+      <c r="I12" s="25"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
@@ -4235,12 +4682,12 @@
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
-      <c r="D13" s="28"/>
+      <c r="D13" s="27"/>
       <c r="E13" s="8"/>
       <c r="F13" s="12"/>
-      <c r="G13" s="29"/>
+      <c r="G13" s="28"/>
       <c r="H13" s="9"/>
-      <c r="I13" s="26"/>
+      <c r="I13" s="25"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
@@ -4248,12 +4695,12 @@
       </c>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
-      <c r="D14" s="28"/>
+      <c r="D14" s="27"/>
       <c r="E14" s="8"/>
       <c r="F14" s="12"/>
-      <c r="G14" s="29"/>
+      <c r="G14" s="28"/>
       <c r="H14" s="9"/>
-      <c r="I14" s="26"/>
+      <c r="I14" s="25"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
@@ -4261,23 +4708,23 @@
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
-      <c r="D15" s="28"/>
+      <c r="D15" s="27"/>
       <c r="E15" s="8"/>
       <c r="F15" s="12"/>
-      <c r="G15" s="29"/>
+      <c r="G15" s="28"/>
       <c r="H15" s="9"/>
-      <c r="I15" s="26"/>
+      <c r="I15" s="25"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
-      <c r="D16" s="28"/>
+      <c r="D16" s="27"/>
       <c r="E16" s="8"/>
       <c r="F16" s="12"/>
-      <c r="G16" s="29"/>
+      <c r="G16" s="28"/>
       <c r="H16" s="9"/>
-      <c r="I16" s="26"/>
+      <c r="I16" s="25"/>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="6"/>
@@ -4288,7 +4735,7 @@
       <c r="F17" s="12"/>
       <c r="G17" s="6"/>
       <c r="H17" s="9"/>
-      <c r="I17" s="26"/>
+      <c r="I17" s="25"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6"/>
@@ -4299,7 +4746,7 @@
       <c r="F18" s="12"/>
       <c r="G18" s="6"/>
       <c r="H18" s="9"/>
-      <c r="I18" s="26"/>
+      <c r="I18" s="25"/>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6"/>
@@ -4310,7 +4757,7 @@
       <c r="F19" s="13"/>
       <c r="G19" s="6"/>
       <c r="H19" s="9"/>
-      <c r="I19" s="26"/>
+      <c r="I19" s="25"/>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6"/>
@@ -4321,7 +4768,7 @@
       <c r="F20" s="15"/>
       <c r="G20" s="6"/>
       <c r="H20" s="9"/>
-      <c r="I20" s="26"/>
+      <c r="I20" s="25"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6"/>
@@ -4729,7 +5176,7 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="43" t="s">
+      <c r="H1" s="42" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="5" t="s">
@@ -4741,232 +5188,232 @@
         <v>9</v>
       </c>
       <c r="B2" s="7"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="24"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="23"/>
       <c r="E2" s="18"/>
       <c r="F2" s="19"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="26"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="25"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="7"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="24"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="23"/>
       <c r="E3" s="18"/>
       <c r="F3" s="19"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="26"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="37"/>
+      <c r="I3" s="25"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="7"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="24"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="23"/>
       <c r="E4" s="18"/>
       <c r="F4" s="19"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="26"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="37"/>
+      <c r="I4" s="25"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="7"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="24"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="23"/>
       <c r="E5" s="18"/>
       <c r="F5" s="19"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="39"/>
-      <c r="I5" s="26"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="38"/>
+      <c r="I5" s="25"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="7"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="24"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="23"/>
       <c r="E6" s="18"/>
       <c r="F6" s="19"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="26"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="25"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="7"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="24"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="23"/>
       <c r="E7" s="18"/>
       <c r="F7" s="19"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="40"/>
-      <c r="I7" s="26"/>
+      <c r="G7" s="43"/>
+      <c r="H7" s="39"/>
+      <c r="I7" s="25"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="7"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="24"/>
+      <c r="C8" s="26"/>
+      <c r="D8" s="23"/>
       <c r="E8" s="18"/>
       <c r="F8" s="19"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="40"/>
-      <c r="I8" s="26"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="39"/>
+      <c r="I8" s="25"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="7"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="24"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="23"/>
       <c r="E9" s="18"/>
       <c r="F9" s="19"/>
-      <c r="G9" s="45"/>
-      <c r="H9" s="38"/>
-      <c r="I9" s="26"/>
+      <c r="G9" s="44"/>
+      <c r="H9" s="37"/>
+      <c r="I9" s="25"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="7"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="24"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="23"/>
       <c r="E10" s="18"/>
       <c r="F10" s="19"/>
-      <c r="G10" s="45"/>
-      <c r="H10" s="38"/>
-      <c r="I10" s="26"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="37"/>
+      <c r="I10" s="25"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="7"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="24"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="23"/>
       <c r="E11" s="18"/>
       <c r="F11" s="19"/>
-      <c r="G11" s="45"/>
-      <c r="H11" s="38"/>
-      <c r="I11" s="26"/>
+      <c r="G11" s="44"/>
+      <c r="H11" s="37"/>
+      <c r="I11" s="25"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B12" s="7"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="24"/>
+      <c r="C12" s="26"/>
+      <c r="D12" s="23"/>
       <c r="E12" s="18"/>
       <c r="F12" s="19"/>
-      <c r="G12" s="45"/>
-      <c r="H12" s="38"/>
-      <c r="I12" s="26"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="37"/>
+      <c r="I12" s="25"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B13" s="7"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="24"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="23"/>
       <c r="E13" s="18"/>
       <c r="F13" s="19"/>
-      <c r="G13" s="45"/>
-      <c r="H13" s="38"/>
-      <c r="I13" s="26"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="37"/>
+      <c r="I13" s="25"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B14" s="7"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="24"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="23"/>
       <c r="E14" s="18"/>
       <c r="F14" s="19"/>
-      <c r="G14" s="45"/>
-      <c r="H14" s="38"/>
-      <c r="I14" s="26"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="37"/>
+      <c r="I14" s="25"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B15" s="7"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="24"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="23"/>
       <c r="E15" s="18"/>
       <c r="F15" s="19"/>
-      <c r="G15" s="45"/>
-      <c r="H15" s="38"/>
-      <c r="I15" s="26"/>
+      <c r="G15" s="44"/>
+      <c r="H15" s="37"/>
+      <c r="I15" s="25"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B16" s="7"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="24"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="23"/>
       <c r="E16" s="18"/>
       <c r="F16" s="12"/>
-      <c r="G16" s="45"/>
-      <c r="H16" s="38"/>
-      <c r="I16" s="26"/>
+      <c r="G16" s="44"/>
+      <c r="H16" s="37"/>
+      <c r="I16" s="25"/>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1">
-      <c r="A17" s="29" t="s">
+      <c r="A17" s="28" t="s">
         <v>9</v>
       </c>
       <c r="B17" s="7"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="24"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="23"/>
       <c r="E17" s="18"/>
       <c r="F17" s="12"/>
-      <c r="G17" s="41"/>
-      <c r="H17" s="38"/>
-      <c r="I17" s="26"/>
+      <c r="G17" s="40"/>
+      <c r="H17" s="37"/>
+      <c r="I17" s="25"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B18" s="7"/>
-      <c r="C18" s="27"/>
-      <c r="D18" s="24"/>
+      <c r="C18" s="26"/>
+      <c r="D18" s="23"/>
       <c r="E18" s="18"/>
       <c r="F18" s="12"/>
-      <c r="G18" s="45"/>
-      <c r="H18" s="38"/>
-      <c r="I18" s="26"/>
+      <c r="G18" s="44"/>
+      <c r="H18" s="37"/>
+      <c r="I18" s="25"/>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6"/>
       <c r="B19" s="8"/>
       <c r="C19" s="7"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="36"/>
-      <c r="G19" s="33"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="33"/>
+      <c r="F19" s="35"/>
+      <c r="G19" s="32"/>
       <c r="H19" s="9"/>
-      <c r="I19" s="26"/>
+      <c r="I19" s="25"/>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6"/>
@@ -4975,9 +5422,9 @@
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
       <c r="F20" s="15"/>
-      <c r="G20" s="33"/>
+      <c r="G20" s="32"/>
       <c r="H20" s="9"/>
-      <c r="I20" s="26"/>
+      <c r="I20" s="25"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6"/>
@@ -4986,9 +5433,9 @@
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
       <c r="F21" s="9"/>
-      <c r="G21" s="33"/>
+      <c r="G21" s="32"/>
       <c r="H21" s="9"/>
-      <c r="I21" s="26"/>
+      <c r="I21" s="25"/>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="6"/>
@@ -4997,9 +5444,9 @@
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
       <c r="F22" s="9"/>
-      <c r="G22" s="33"/>
+      <c r="G22" s="32"/>
       <c r="H22" s="9"/>
-      <c r="I22" s="26"/>
+      <c r="I22" s="25"/>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="6"/>
@@ -5008,9 +5455,9 @@
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
       <c r="F23" s="9"/>
-      <c r="G23" s="33"/>
+      <c r="G23" s="32"/>
       <c r="H23" s="9"/>
-      <c r="I23" s="26"/>
+      <c r="I23" s="25"/>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="6"/>
@@ -5019,9 +5466,9 @@
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
       <c r="F24" s="9"/>
-      <c r="G24" s="33"/>
+      <c r="G24" s="32"/>
       <c r="H24" s="9"/>
-      <c r="I24" s="26"/>
+      <c r="I24" s="25"/>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="6"/>
@@ -5032,7 +5479,7 @@
       <c r="F25" s="9"/>
       <c r="G25" s="6"/>
       <c r="H25" s="9"/>
-      <c r="I25" s="26"/>
+      <c r="I25" s="25"/>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="6"/>
@@ -5043,7 +5490,7 @@
       <c r="F26" s="9"/>
       <c r="G26" s="6"/>
       <c r="H26" s="9"/>
-      <c r="I26" s="26"/>
+      <c r="I26" s="25"/>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="6"/>
@@ -5054,7 +5501,7 @@
       <c r="F27" s="9"/>
       <c r="G27" s="6"/>
       <c r="H27" s="9"/>
-      <c r="I27" s="26"/>
+      <c r="I27" s="25"/>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="6"/>
@@ -5065,7 +5512,7 @@
       <c r="F28" s="9"/>
       <c r="G28" s="6"/>
       <c r="H28" s="9"/>
-      <c r="I28" s="26"/>
+      <c r="I28" s="25"/>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="6"/>
@@ -5076,7 +5523,7 @@
       <c r="F29" s="9"/>
       <c r="G29" s="6"/>
       <c r="H29" s="9"/>
-      <c r="I29" s="26"/>
+      <c r="I29" s="25"/>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="6"/>
@@ -5087,7 +5534,7 @@
       <c r="F30" s="9"/>
       <c r="G30" s="6"/>
       <c r="H30" s="9"/>
-      <c r="I30" s="26"/>
+      <c r="I30" s="25"/>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="6"/>
@@ -5098,7 +5545,7 @@
       <c r="F31" s="9"/>
       <c r="G31" s="6"/>
       <c r="H31" s="9"/>
-      <c r="I31" s="26"/>
+      <c r="I31" s="25"/>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="6"/>
@@ -5109,7 +5556,7 @@
       <c r="F32" s="9"/>
       <c r="G32" s="6"/>
       <c r="H32" s="9"/>
-      <c r="I32" s="26"/>
+      <c r="I32" s="25"/>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="6"/>
@@ -5120,7 +5567,7 @@
       <c r="F33" s="9"/>
       <c r="G33" s="6"/>
       <c r="H33" s="9"/>
-      <c r="I33" s="26"/>
+      <c r="I33" s="25"/>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="6"/>
@@ -5131,7 +5578,7 @@
       <c r="F34" s="9"/>
       <c r="G34" s="6"/>
       <c r="H34" s="9"/>
-      <c r="I34" s="26"/>
+      <c r="I34" s="25"/>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="6"/>
@@ -5142,7 +5589,7 @@
       <c r="F35" s="9"/>
       <c r="G35" s="6"/>
       <c r="H35" s="9"/>
-      <c r="I35" s="26"/>
+      <c r="I35" s="25"/>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="6"/>
@@ -5431,63 +5878,63 @@
         <v>9</v>
       </c>
       <c r="B2" s="7"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="24"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="23"/>
       <c r="E2" s="18"/>
       <c r="F2" s="12"/>
       <c r="G2" s="20"/>
       <c r="H2" s="9"/>
-      <c r="I2" s="26"/>
+      <c r="I2" s="25"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="7"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="24"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="23"/>
       <c r="E3" s="18"/>
       <c r="F3" s="12"/>
       <c r="G3" s="20"/>
       <c r="H3" s="9"/>
-      <c r="I3" s="37"/>
+      <c r="I3" s="36"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="7"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="24"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="23"/>
       <c r="E4" s="18"/>
       <c r="F4" s="12"/>
       <c r="G4" s="20"/>
       <c r="H4" s="9"/>
-      <c r="I4" s="26"/>
+      <c r="I4" s="25"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="7"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="24"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="23"/>
       <c r="E5" s="18"/>
       <c r="F5" s="12"/>
       <c r="G5" s="20"/>
       <c r="H5" s="9"/>
-      <c r="I5" s="26"/>
+      <c r="I5" s="25"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="35"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="34"/>
       <c r="G6" s="6"/>
       <c r="H6" s="9"/>
-      <c r="I6" s="26"/>
+      <c r="I6" s="25"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6"/>
@@ -6641,6 +7088,58 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-496593</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-496593</Url>
+      <Description>QAFFA7D2F2TC-2102087286-496593</Description>
+    </_dlc_DocIdUrl>
+    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </DossierOwner>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ccca9d190a3c43e89f73773ee806c8b5>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ia4b831ccad64069ad2e0cbd870e9b8a>
+    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </alteradopor>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="44" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ac14f8cb44178d381f4c0afb30680a90">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5e58414b065c9b590c40efa77cd84bb6" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -7018,58 +7517,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-496593</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-496593</Url>
-      <Description>QAFFA7D2F2TC-2102087286-496593</Description>
-    </_dlc_DocIdUrl>
-    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </DossierOwner>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ccca9d190a3c43e89f73773ee806c8b5>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ia4b831ccad64069ad2e0cbd870e9b8a>
-    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </alteradopor>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
@@ -7121,7 +7568,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32450128-80FB-4462-BDF1-414021F91FB7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7129,7 +7576,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32450128-80FB-4462-BDF1-414021F91FB7}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas 06.10.2025 a 12.10.2025.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas 06.10.2025 a 12.10.2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms.sharepoint.com/teams/BR0010-4356589/Shared Documents/BACK-OFFICE SME/Santander/2025/Relatório de Recusas/05. Maio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{043F0B9B-CCFD-48B2-886B-736816539870}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F20489CC-7DC9-400B-8F83-DCFE2EC5C0B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="06.10" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="193">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -463,6 +463,201 @@
   </si>
   <si>
     <t xml:space="preserve">LIVIA PIRILLO GRECCHI                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DANIEL AUGUSTO GARCIA DOS SANTOS             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Falta de vistoria </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JULIO CESAR LEMES DE SOUZA                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUZIA ALVES DE SOUZA FERREIRA                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARMO MARQUES BIALY                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HENRIQUE DE BARROS DIVINO                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUIZ EDUARDO SILVA NASCIMENTO                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JEFFERSON HENRIQUE DIAS SA                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLAUDIO DOS SANTOS                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALEXIA RENATA AZEVEDO                        </t>
+  </si>
+  <si>
+    <t>C
+BE bonificação está incorreta, apólice anterior consta classe de b
+ônus 0, não havendo sinistro, conforme regra concede 1 classe de b
+ônus, assim sendo o correto bônus 1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SACOLAO JL LTDA ME                           </t>
+  </si>
+  <si>
+    <t>FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAULO ROBERTO GARCIA SANTOS                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCIO JOSE COELHO DA LUZ                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HAINER MAIA PINHEIRO                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA CLARA MAESTRI ME                       </t>
+  </si>
+  <si>
+    <t>Fotos que tiveram repique: Frente e lateral do passageiro, Frente e lateral do motorista, Traseira e lateral do motorista, Traseira e lateral do passageiro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LABORATORIO LEAL LTDA ME                     </t>
+  </si>
+  <si>
+    <t>Fotos que tiveram repique: Chassi FRUSTRADA: CLIENTE NÃO CORRIGIU A FOTO INCORRETA - PRAZO EXPIRADO.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDUARDO FERREIRA DOS SANTOS                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIGUEL ANTONIO NETO                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDILAINE APARECIDA DE SOUZA FANTUCCI         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUCIANO MATIAS SOARES                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANTONIO DOMINGUES GRACA FILHO                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALESSANDRO SILVA FREIRE                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DANILO TADEU DUARTE                          </t>
+  </si>
+  <si>
+    <t>NUP CANCELAMENTO 08/10/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RENATO SILVA DE ARRUDA                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HIPOWER SEGURANCA ELETRONICA LTDA ME         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARYEL FERREIRA LAURENTINO                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROSA CRISTINA PERES DOS SANTOS FERNANDES     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEDA DOS SANTOS ROCHA NASCIMENTO             </t>
+  </si>
+  <si>
+    <t>Nup CANCELAMENTO 08/10/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDRE LUIZ SANTOS ANDRADE                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JILVANIA DA SILVA MOREIRA                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANA CLAUDIA PANTOJA FRANCO                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALENILDA ROCHA MACIEL GOIS                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VIVIANI MASSARO                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIRCEU CORSO                                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLAUDIA ALESSANDRA PINHEIRO GUIMARAES        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALEX FELIX SHAER                             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SILVIA CRISTINA VIEIRA DA SILVA              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DANRLEI DAHMER                               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROZIEL SANTOS RIBEIRO                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAULO HENRIQUE PARO CAMARGO                  </t>
+  </si>
+  <si>
+    <t>LORENZONI COMERCIO DE ELETRONICOS E VARIEDADE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JEAN PATRICK MOREIRA DA SILVA                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCIA OSCARLINA BORGES                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANTONIO CESAR FERNANDES                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUIZ DONIZETI CARNEIRO                       </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, a apólice foi renovada na
+congênere de origem, portanto peço a gentileza de encaminhar a do
+cumentação abaixo, para análise.&lt;br&gt;Cópia da apólice congênere com
+vigência de 2025 à 2026 e Endosso de cancelamento emitido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE ALMIRO DE LIMA COSTA ME                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMILA JORGE MARTINS                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANNAS TRANSPORTES E SERVICOS LTDA           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLAUDIA MARCIA DE SOUZA SANTOS TAVARES       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DANILO BALBINOTTI GIGLIOLI                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOAO ROBERTO DELA MARTA                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DANYLLO ALESSANDRO VAN SOEST                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVANDRO JOSE BALBINO                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FERNANDO BATISTA DOS SANTOS                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCOS SILVA DE SOUZA                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLAVIO DA CRUZ FAUSTINO                      </t>
   </si>
 </sst>
 </file>
@@ -763,7 +958,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -917,6 +1112,26 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4490,7 +4705,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BF216D7-F2B3-4C54-A7B9-7048B06C2C75}">
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
@@ -4537,600 +4752,1695 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="25"/>
+      <c r="B2" s="7">
+        <v>45930</v>
+      </c>
+      <c r="C2" s="26">
+        <v>45939</v>
+      </c>
+      <c r="D2" s="23">
+        <v>134696628</v>
+      </c>
+      <c r="E2" s="18">
+        <v>3450094395</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="G2" s="64" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="66" t="s">
+        <v>131</v>
+      </c>
+      <c r="I2" s="50">
+        <v>45930</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="25"/>
+      <c r="B3" s="7">
+        <v>45926</v>
+      </c>
+      <c r="C3" s="26">
+        <v>45939</v>
+      </c>
+      <c r="D3" s="23">
+        <v>134705802</v>
+      </c>
+      <c r="E3" s="18">
+        <v>3450091755</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="G3" s="64" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="66" t="s">
+        <v>131</v>
+      </c>
+      <c r="I3" s="50">
+        <v>45926</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="25"/>
+      <c r="B4" s="7">
+        <v>45926</v>
+      </c>
+      <c r="C4" s="26">
+        <v>45939</v>
+      </c>
+      <c r="D4" s="23">
+        <v>134705973</v>
+      </c>
+      <c r="E4" s="18">
+        <v>3450092052</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="G4" s="64" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" s="66" t="s">
+        <v>131</v>
+      </c>
+      <c r="I4" s="50">
+        <v>45926</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="25"/>
+      <c r="B5" s="7">
+        <v>45930</v>
+      </c>
+      <c r="C5" s="26">
+        <v>45939</v>
+      </c>
+      <c r="D5" s="23">
+        <v>134714627</v>
+      </c>
+      <c r="E5" s="18">
+        <v>3450095759</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="G5" s="64" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="66" t="s">
+        <v>131</v>
+      </c>
+      <c r="I5" s="50">
+        <v>45930</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="25"/>
+      <c r="B6" s="7">
+        <v>45930</v>
+      </c>
+      <c r="C6" s="26">
+        <v>45939</v>
+      </c>
+      <c r="D6" s="23">
+        <v>134705558</v>
+      </c>
+      <c r="E6" s="18">
+        <v>3450095011</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="G6" s="64" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="66" t="s">
+        <v>131</v>
+      </c>
+      <c r="I6" s="50">
+        <v>45930</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="27"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="25"/>
+      <c r="B7" s="7">
+        <v>45930</v>
+      </c>
+      <c r="C7" s="26">
+        <v>45939</v>
+      </c>
+      <c r="D7" s="23">
+        <v>134711717</v>
+      </c>
+      <c r="E7" s="18">
+        <v>3450095385</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="G7" s="64" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7" s="66" t="s">
+        <v>131</v>
+      </c>
+      <c r="I7" s="50">
+        <v>45930</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="25"/>
+      <c r="B8" s="7">
+        <v>45930</v>
+      </c>
+      <c r="C8" s="26">
+        <v>45939</v>
+      </c>
+      <c r="D8" s="23">
+        <v>134713506</v>
+      </c>
+      <c r="E8" s="18">
+        <v>3450095627</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="G8" s="64" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" s="66" t="s">
+        <v>131</v>
+      </c>
+      <c r="I8" s="50">
+        <v>45930</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="25"/>
+      <c r="B9" s="7">
+        <v>45930</v>
+      </c>
+      <c r="C9" s="26">
+        <v>45939</v>
+      </c>
+      <c r="D9" s="23">
+        <v>134714325</v>
+      </c>
+      <c r="E9" s="18">
+        <v>3450095704</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="G9" s="64" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" s="66" t="s">
+        <v>131</v>
+      </c>
+      <c r="I9" s="50">
+        <v>45930</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="25"/>
+      <c r="B10" s="7">
+        <v>45926</v>
+      </c>
+      <c r="C10" s="26">
+        <v>45939</v>
+      </c>
+      <c r="D10" s="23">
+        <v>134701829</v>
+      </c>
+      <c r="E10" s="18">
+        <v>3450092228</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="G10" s="64" t="s">
+        <v>17</v>
+      </c>
+      <c r="H10" s="66" t="s">
+        <v>131</v>
+      </c>
+      <c r="I10" s="50">
+        <v>45926</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="28"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="25"/>
+      <c r="B11" s="7">
+        <v>45960</v>
+      </c>
+      <c r="C11" s="26">
+        <v>45939</v>
+      </c>
+      <c r="D11" s="23">
+        <v>134716592</v>
+      </c>
+      <c r="E11" s="18">
+        <v>3450095990</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="G11" s="64" t="s">
+        <v>11</v>
+      </c>
+      <c r="H11" s="69" t="s">
+        <v>140</v>
+      </c>
+      <c r="I11" s="50">
+        <v>45936</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="28"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="25"/>
+      <c r="B12" s="7">
+        <v>45931</v>
+      </c>
+      <c r="C12" s="26">
+        <v>45939</v>
+      </c>
+      <c r="D12" s="23">
+        <v>134720289</v>
+      </c>
+      <c r="E12" s="18">
+        <v>3450096056</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="G12" s="64" t="s">
+        <v>27</v>
+      </c>
+      <c r="H12" s="66" t="s">
+        <v>142</v>
+      </c>
+      <c r="I12" s="50">
+        <v>45931</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="27"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="25"/>
+      <c r="B13" s="7">
+        <v>45930</v>
+      </c>
+      <c r="C13" s="26">
+        <v>45939</v>
+      </c>
+      <c r="D13" s="23">
+        <v>134704471</v>
+      </c>
+      <c r="E13" s="18">
+        <v>3450094923</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="G13" s="64" t="s">
+        <v>17</v>
+      </c>
+      <c r="H13" s="66" t="s">
+        <v>131</v>
+      </c>
+      <c r="I13" s="50">
+        <v>45930</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="27"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="28"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="25"/>
+      <c r="B14" s="7">
+        <v>45931</v>
+      </c>
+      <c r="C14" s="26">
+        <v>45939</v>
+      </c>
+      <c r="D14" s="23">
+        <v>134721001</v>
+      </c>
+      <c r="E14" s="18">
+        <v>3450096090</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="G14" s="64" t="s">
+        <v>17</v>
+      </c>
+      <c r="H14" s="66" t="s">
+        <v>131</v>
+      </c>
+      <c r="I14" s="50">
+        <v>45931</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="27"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="25"/>
+      <c r="B15" s="7">
+        <v>45931</v>
+      </c>
+      <c r="C15" s="26">
+        <v>45939</v>
+      </c>
+      <c r="D15" s="23">
+        <v>134731096</v>
+      </c>
+      <c r="E15" s="18">
+        <v>3450096738</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G15" s="64" t="s">
+        <v>17</v>
+      </c>
+      <c r="H15" s="66" t="s">
+        <v>131</v>
+      </c>
+      <c r="I15" s="50">
+        <v>45931</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="6"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="28"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="25"/>
+      <c r="A16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="7">
+        <v>45931</v>
+      </c>
+      <c r="C16" s="26">
+        <v>45939</v>
+      </c>
+      <c r="D16" s="23">
+        <v>134739126</v>
+      </c>
+      <c r="E16" s="18">
+        <v>3450097190</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="G16" s="65" t="s">
+        <v>27</v>
+      </c>
+      <c r="H16" s="66" t="s">
+        <v>147</v>
+      </c>
+      <c r="I16" s="50">
+        <v>45931</v>
+      </c>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="6"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="25"/>
+      <c r="A17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="7">
+        <v>45931</v>
+      </c>
+      <c r="C17" s="26">
+        <v>45939</v>
+      </c>
+      <c r="D17" s="23">
+        <v>134721872</v>
+      </c>
+      <c r="E17" s="18">
+        <v>3450096144</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="G17" s="65" t="s">
+        <v>27</v>
+      </c>
+      <c r="H17" s="66" t="s">
+        <v>149</v>
+      </c>
+      <c r="I17" s="50">
+        <v>45931</v>
+      </c>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="6"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="25"/>
+      <c r="A18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="7">
+        <v>45931</v>
+      </c>
+      <c r="C18" s="26">
+        <v>45939</v>
+      </c>
+      <c r="D18" s="23">
+        <v>134725472</v>
+      </c>
+      <c r="E18" s="18">
+        <v>3450096463</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="G18" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H18" s="66" t="s">
+        <v>131</v>
+      </c>
+      <c r="I18" s="50">
+        <v>45931</v>
+      </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="6"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="25"/>
+      <c r="A19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="7">
+        <v>45931</v>
+      </c>
+      <c r="C19" s="26">
+        <v>45939</v>
+      </c>
+      <c r="D19" s="23">
+        <v>134733874</v>
+      </c>
+      <c r="E19" s="18">
+        <v>3450096980</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="G19" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H19" s="66" t="s">
+        <v>131</v>
+      </c>
+      <c r="I19" s="50">
+        <v>45931</v>
+      </c>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="6"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="25"/>
+      <c r="A20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="7">
+        <v>45926</v>
+      </c>
+      <c r="C20" s="26">
+        <v>45939</v>
+      </c>
+      <c r="D20" s="23">
+        <v>134702759</v>
+      </c>
+      <c r="E20" s="18">
+        <v>3450091898</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="G20" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H20" s="66" t="s">
+        <v>131</v>
+      </c>
+      <c r="I20" s="50">
+        <v>45926</v>
+      </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="6"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="9"/>
+      <c r="A21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="7">
+        <v>45930</v>
+      </c>
+      <c r="C21" s="26">
+        <v>45939</v>
+      </c>
+      <c r="D21" s="23">
+        <v>134710734</v>
+      </c>
+      <c r="E21" s="18">
+        <v>3450095320</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="G21" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H21" s="66" t="s">
+        <v>131</v>
+      </c>
+      <c r="I21" s="50">
+        <v>45930</v>
+      </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="6"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="9"/>
+      <c r="A22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="7">
+        <v>45930</v>
+      </c>
+      <c r="C22" s="26">
+        <v>45939</v>
+      </c>
+      <c r="D22" s="23">
+        <v>134707685</v>
+      </c>
+      <c r="E22" s="18">
+        <v>3450095187</v>
+      </c>
+      <c r="F22" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="G22" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H22" s="66" t="s">
+        <v>131</v>
+      </c>
+      <c r="I22" s="50">
+        <v>45960</v>
+      </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="6"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="9"/>
+      <c r="A23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="7">
+        <v>45930</v>
+      </c>
+      <c r="C23" s="26">
+        <v>45939</v>
+      </c>
+      <c r="D23" s="23">
+        <v>134700667</v>
+      </c>
+      <c r="E23" s="18">
+        <v>3450094660</v>
+      </c>
+      <c r="F23" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="G23" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H23" s="66" t="s">
+        <v>131</v>
+      </c>
+      <c r="I23" s="50">
+        <v>45930</v>
+      </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="6"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="9"/>
+      <c r="A24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="7">
+        <v>45941</v>
+      </c>
+      <c r="C24" s="26">
+        <v>45939</v>
+      </c>
+      <c r="D24" s="23">
+        <v>134797684</v>
+      </c>
+      <c r="E24" s="18">
+        <v>3450099961</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="G24" s="65" t="s">
+        <v>38</v>
+      </c>
+      <c r="H24" s="66" t="s">
+        <v>157</v>
+      </c>
+      <c r="I24" s="50">
+        <v>45938</v>
+      </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="6"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="9"/>
+      <c r="A25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="7">
+        <v>45937</v>
+      </c>
+      <c r="C25" s="26">
+        <v>45939</v>
+      </c>
+      <c r="D25" s="23">
+        <v>134825913</v>
+      </c>
+      <c r="E25" s="18">
+        <v>3450101039</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="G25" s="65" t="s">
+        <v>14</v>
+      </c>
+      <c r="H25" s="66" t="s">
+        <v>20</v>
+      </c>
+      <c r="I25" s="50">
+        <v>45937</v>
+      </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="6"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="9"/>
+      <c r="A26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="7">
+        <v>45937</v>
+      </c>
+      <c r="C26" s="26">
+        <v>45939</v>
+      </c>
+      <c r="D26" s="23">
+        <v>134826970</v>
+      </c>
+      <c r="E26" s="18">
+        <v>3450101259</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="G26" s="65" t="s">
+        <v>14</v>
+      </c>
+      <c r="H26" s="66" t="s">
+        <v>20</v>
+      </c>
+      <c r="I26" s="50">
+        <v>45937</v>
+      </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="6"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="9"/>
+      <c r="A27" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="7">
+        <v>45931</v>
+      </c>
+      <c r="C27" s="26">
+        <v>45939</v>
+      </c>
+      <c r="D27" s="23">
+        <v>134735996</v>
+      </c>
+      <c r="E27" s="18">
+        <v>3450097068</v>
+      </c>
+      <c r="F27" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="G27" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H27" s="66" t="s">
+        <v>131</v>
+      </c>
+      <c r="I27" s="50">
+        <v>45931</v>
+      </c>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="6"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="9"/>
+      <c r="A28" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="7">
+        <v>45930</v>
+      </c>
+      <c r="C28" s="26">
+        <v>45939</v>
+      </c>
+      <c r="D28" s="23">
+        <v>134700854</v>
+      </c>
+      <c r="E28" s="18">
+        <v>3450094670</v>
+      </c>
+      <c r="F28" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="G28" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H28" s="66" t="s">
+        <v>131</v>
+      </c>
+      <c r="I28" s="50">
+        <v>45930</v>
+      </c>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="6"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="9"/>
+      <c r="A29" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="7">
+        <v>45938</v>
+      </c>
+      <c r="C29" s="26">
+        <v>45939</v>
+      </c>
+      <c r="D29" s="23">
+        <v>134833192</v>
+      </c>
+      <c r="E29" s="18">
+        <v>3450101336</v>
+      </c>
+      <c r="F29" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="G29" s="65" t="s">
+        <v>38</v>
+      </c>
+      <c r="H29" s="66" t="s">
+        <v>163</v>
+      </c>
+      <c r="I29" s="50">
+        <v>45938</v>
+      </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="6"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="9"/>
+      <c r="A30" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="7">
+        <v>45938</v>
+      </c>
+      <c r="C30" s="26">
+        <v>45939</v>
+      </c>
+      <c r="D30" s="23">
+        <v>134839517</v>
+      </c>
+      <c r="E30" s="18">
+        <v>3450101743</v>
+      </c>
+      <c r="F30" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="G30" s="65" t="s">
+        <v>14</v>
+      </c>
+      <c r="H30" s="66" t="s">
+        <v>20</v>
+      </c>
+      <c r="I30" s="50">
+        <v>45938</v>
+      </c>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="6"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="9"/>
+      <c r="A31" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" s="7">
+        <v>45930</v>
+      </c>
+      <c r="C31" s="26">
+        <v>45939</v>
+      </c>
+      <c r="D31" s="23">
+        <v>134712612</v>
+      </c>
+      <c r="E31" s="18">
+        <v>3450095495</v>
+      </c>
+      <c r="F31" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="G31" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H31" s="66" t="s">
+        <v>131</v>
+      </c>
+      <c r="I31" s="50">
+        <v>45930</v>
+      </c>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="6"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="9"/>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="6"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="9"/>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="6"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="9"/>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="6"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="9"/>
-    </row>
-    <row r="36" spans="1:8">
-      <c r="A36" s="6"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="9"/>
-    </row>
-    <row r="37" spans="1:8">
-      <c r="A37" s="6"/>
-      <c r="B37" s="8"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="9"/>
-    </row>
-    <row r="38" spans="1:8">
-      <c r="A38" s="6"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="9"/>
-    </row>
-    <row r="39" spans="1:8">
-      <c r="A39" s="6"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="9"/>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="6"/>
-      <c r="B40" s="8"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="9"/>
-    </row>
-    <row r="41" spans="1:8">
-      <c r="A41" s="6"/>
-      <c r="B41" s="8"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="6"/>
-      <c r="H41" s="9"/>
-    </row>
-    <row r="42" spans="1:8">
-      <c r="A42" s="6"/>
-      <c r="B42" s="8"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="9"/>
-    </row>
-    <row r="43" spans="1:8">
-      <c r="A43" s="6"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="9"/>
-    </row>
-    <row r="44" spans="1:8">
-      <c r="A44" s="6"/>
-      <c r="B44" s="8"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="6"/>
-      <c r="H44" s="9"/>
-    </row>
-    <row r="45" spans="1:8">
-      <c r="A45" s="6"/>
-      <c r="B45" s="8"/>
-      <c r="C45" s="7"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="6"/>
-      <c r="H45" s="9"/>
-    </row>
-    <row r="46" spans="1:8">
-      <c r="A46" s="6"/>
-      <c r="B46" s="8"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="9"/>
-      <c r="G46" s="6"/>
-      <c r="H46" s="9"/>
-    </row>
-    <row r="47" spans="1:8">
-      <c r="A47" s="6"/>
-      <c r="B47" s="8"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="9"/>
-      <c r="G47" s="6"/>
-      <c r="H47" s="9"/>
-    </row>
-    <row r="48" spans="1:8">
-      <c r="A48" s="6"/>
-      <c r="B48" s="8"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="9"/>
-      <c r="G48" s="6"/>
-      <c r="H48" s="9"/>
-    </row>
-    <row r="49" spans="1:8">
-      <c r="A49" s="6"/>
-      <c r="B49" s="8"/>
-      <c r="C49" s="7"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="9"/>
-      <c r="G49" s="6"/>
-      <c r="H49" s="9"/>
-    </row>
-    <row r="50" spans="1:8">
-      <c r="A50" s="6"/>
-      <c r="B50" s="8"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="9"/>
-    </row>
-    <row r="51" spans="1:8">
-      <c r="A51" s="6"/>
-      <c r="B51" s="8"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
-      <c r="F51" s="9"/>
-      <c r="G51" s="6"/>
-      <c r="H51" s="9"/>
-    </row>
-    <row r="52" spans="1:8">
-      <c r="A52" s="6"/>
-      <c r="B52" s="8"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="9"/>
-      <c r="G52" s="6"/>
-      <c r="H52" s="9"/>
-    </row>
-    <row r="53" spans="1:8">
-      <c r="A53" s="6"/>
-      <c r="B53" s="8"/>
-      <c r="C53" s="7"/>
-      <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
-      <c r="F53" s="9"/>
-      <c r="G53" s="6"/>
-      <c r="H53" s="9"/>
-    </row>
-    <row r="54" spans="1:8">
-      <c r="A54" s="6"/>
-      <c r="B54" s="8"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="6"/>
-      <c r="H54" s="9"/>
-    </row>
-    <row r="55" spans="1:8">
-      <c r="A55" s="6"/>
-      <c r="B55" s="8"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="6"/>
-      <c r="H55" s="9"/>
+      <c r="A32" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" s="7">
+        <v>45926</v>
+      </c>
+      <c r="C32" s="26">
+        <v>45939</v>
+      </c>
+      <c r="D32" s="23">
+        <v>134661083</v>
+      </c>
+      <c r="E32" s="18">
+        <v>3450092294</v>
+      </c>
+      <c r="F32" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="G32" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H32" s="66" t="s">
+        <v>131</v>
+      </c>
+      <c r="I32" s="50">
+        <v>45926</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" s="7">
+        <v>45929</v>
+      </c>
+      <c r="C33" s="26">
+        <v>45939</v>
+      </c>
+      <c r="D33" s="23">
+        <v>134704437</v>
+      </c>
+      <c r="E33" s="18">
+        <v>3450094175</v>
+      </c>
+      <c r="F33" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="G33" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H33" s="66" t="s">
+        <v>131</v>
+      </c>
+      <c r="I33" s="50">
+        <v>45929</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B34" s="7">
+        <v>45930</v>
+      </c>
+      <c r="C34" s="26">
+        <v>45939</v>
+      </c>
+      <c r="D34" s="23">
+        <v>134707055</v>
+      </c>
+      <c r="E34" s="18">
+        <v>3450095143</v>
+      </c>
+      <c r="F34" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="G34" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H34" s="66" t="s">
+        <v>131</v>
+      </c>
+      <c r="I34" s="50">
+        <v>45930</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B35" s="7">
+        <v>45929</v>
+      </c>
+      <c r="C35" s="26">
+        <v>45939</v>
+      </c>
+      <c r="D35" s="23">
+        <v>134708678</v>
+      </c>
+      <c r="E35" s="18">
+        <v>3450093559</v>
+      </c>
+      <c r="F35" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="G35" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H35" s="66" t="s">
+        <v>131</v>
+      </c>
+      <c r="I35" s="50">
+        <v>45929</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B36" s="7">
+        <v>45930</v>
+      </c>
+      <c r="C36" s="26">
+        <v>45939</v>
+      </c>
+      <c r="D36" s="23">
+        <v>134709137</v>
+      </c>
+      <c r="E36" s="18">
+        <v>3450095209</v>
+      </c>
+      <c r="F36" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="G36" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H36" s="66" t="s">
+        <v>131</v>
+      </c>
+      <c r="I36" s="50">
+        <v>45930</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B37" s="7">
+        <v>45930</v>
+      </c>
+      <c r="C37" s="26">
+        <v>45939</v>
+      </c>
+      <c r="D37" s="23">
+        <v>134710928</v>
+      </c>
+      <c r="E37" s="18">
+        <v>3450095341</v>
+      </c>
+      <c r="F37" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="G37" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H37" s="66" t="s">
+        <v>131</v>
+      </c>
+      <c r="I37" s="50">
+        <v>45930</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B38" s="7">
+        <v>45930</v>
+      </c>
+      <c r="C38" s="26">
+        <v>45939</v>
+      </c>
+      <c r="D38" s="23">
+        <v>134711937</v>
+      </c>
+      <c r="E38" s="18">
+        <v>3450095407</v>
+      </c>
+      <c r="F38" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="G38" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H38" s="66" t="s">
+        <v>131</v>
+      </c>
+      <c r="I38" s="50">
+        <v>45930</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B39" s="7">
+        <v>45930</v>
+      </c>
+      <c r="C39" s="26">
+        <v>45939</v>
+      </c>
+      <c r="D39" s="23">
+        <v>134712402</v>
+      </c>
+      <c r="E39" s="18">
+        <v>3450095440</v>
+      </c>
+      <c r="F39" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="G39" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H39" s="66" t="s">
+        <v>131</v>
+      </c>
+      <c r="I39" s="50">
+        <v>45930</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B40" s="7">
+        <v>45930</v>
+      </c>
+      <c r="C40" s="26">
+        <v>45939</v>
+      </c>
+      <c r="D40" s="23">
+        <v>134713194</v>
+      </c>
+      <c r="E40" s="18">
+        <v>3450095550</v>
+      </c>
+      <c r="F40" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="G40" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H40" s="66" t="s">
+        <v>131</v>
+      </c>
+      <c r="I40" s="50">
+        <v>45930</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B41" s="7">
+        <v>45926</v>
+      </c>
+      <c r="C41" s="26">
+        <v>45939</v>
+      </c>
+      <c r="D41" s="23">
+        <v>134713216</v>
+      </c>
+      <c r="E41" s="18">
+        <v>3450092349</v>
+      </c>
+      <c r="F41" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="G41" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H41" s="66" t="s">
+        <v>131</v>
+      </c>
+      <c r="I41" s="50">
+        <v>45926</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B42" s="7">
+        <v>45930</v>
+      </c>
+      <c r="C42" s="26">
+        <v>45939</v>
+      </c>
+      <c r="D42" s="23">
+        <v>134714456</v>
+      </c>
+      <c r="E42" s="18">
+        <v>3450095715</v>
+      </c>
+      <c r="F42" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="G42" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H42" s="66" t="s">
+        <v>131</v>
+      </c>
+      <c r="I42" s="50">
+        <v>45930</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B43" s="7">
+        <v>45930</v>
+      </c>
+      <c r="C43" s="26">
+        <v>45939</v>
+      </c>
+      <c r="D43" s="23">
+        <v>134714566</v>
+      </c>
+      <c r="E43" s="18">
+        <v>3450095737</v>
+      </c>
+      <c r="F43" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="G43" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H43" s="66" t="s">
+        <v>131</v>
+      </c>
+      <c r="I43" s="50">
+        <v>45930</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B44" s="7">
+        <v>45930</v>
+      </c>
+      <c r="C44" s="26">
+        <v>45939</v>
+      </c>
+      <c r="D44" s="23">
+        <v>134714660</v>
+      </c>
+      <c r="E44" s="18">
+        <v>3450095760</v>
+      </c>
+      <c r="F44" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="G44" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H44" s="66" t="s">
+        <v>131</v>
+      </c>
+      <c r="I44" s="50">
+        <v>45930</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B45" s="7">
+        <v>45930</v>
+      </c>
+      <c r="C45" s="26">
+        <v>45939</v>
+      </c>
+      <c r="D45" s="23">
+        <v>134714887</v>
+      </c>
+      <c r="E45" s="18">
+        <v>3450095781</v>
+      </c>
+      <c r="F45" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="G45" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H45" s="66" t="s">
+        <v>131</v>
+      </c>
+      <c r="I45" s="50">
+        <v>45930</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B46" s="7">
+        <v>45930</v>
+      </c>
+      <c r="C46" s="26">
+        <v>45939</v>
+      </c>
+      <c r="D46" s="23">
+        <v>134715302</v>
+      </c>
+      <c r="E46" s="18">
+        <v>3450095814</v>
+      </c>
+      <c r="F46" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="G46" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H46" s="66" t="s">
+        <v>131</v>
+      </c>
+      <c r="I46" s="50">
+        <v>45930</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B47" s="7">
+        <v>45930</v>
+      </c>
+      <c r="C47" s="26">
+        <v>45939</v>
+      </c>
+      <c r="D47" s="23">
+        <v>134715732</v>
+      </c>
+      <c r="E47" s="18">
+        <v>3450095880</v>
+      </c>
+      <c r="F47" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="G47" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H47" s="66" t="s">
+        <v>131</v>
+      </c>
+      <c r="I47" s="50">
+        <v>45930</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B48" s="7">
+        <v>45926</v>
+      </c>
+      <c r="C48" s="26">
+        <v>45939</v>
+      </c>
+      <c r="D48" s="23">
+        <v>134667986</v>
+      </c>
+      <c r="E48" s="18">
+        <v>3450092789</v>
+      </c>
+      <c r="F48" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="G48" s="65" t="s">
+        <v>11</v>
+      </c>
+      <c r="H48" s="69" t="s">
+        <v>181</v>
+      </c>
+      <c r="I48" s="50">
+        <v>45931</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B49" s="7">
+        <v>45939</v>
+      </c>
+      <c r="C49" s="26">
+        <v>45939</v>
+      </c>
+      <c r="D49" s="23">
+        <v>134857082</v>
+      </c>
+      <c r="E49" s="18">
+        <v>3450102678</v>
+      </c>
+      <c r="F49" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="G49" s="65" t="s">
+        <v>14</v>
+      </c>
+      <c r="H49" s="66" t="s">
+        <v>20</v>
+      </c>
+      <c r="I49" s="50">
+        <v>45939</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="A50" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B50" s="7">
+        <v>45931</v>
+      </c>
+      <c r="C50" s="26">
+        <v>45939</v>
+      </c>
+      <c r="D50" s="23">
+        <v>134722366</v>
+      </c>
+      <c r="E50" s="18">
+        <v>3450096177</v>
+      </c>
+      <c r="F50" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="G50" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H50" s="66" t="s">
+        <v>131</v>
+      </c>
+      <c r="I50" s="50">
+        <v>45931</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B51" s="7">
+        <v>45931</v>
+      </c>
+      <c r="C51" s="26">
+        <v>45939</v>
+      </c>
+      <c r="D51" s="23">
+        <v>134724022</v>
+      </c>
+      <c r="E51" s="18">
+        <v>3450096310</v>
+      </c>
+      <c r="F51" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="G51" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H51" s="66" t="s">
+        <v>131</v>
+      </c>
+      <c r="I51" s="50">
+        <v>45931</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
+      <c r="A52" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B52" s="7">
+        <v>45931</v>
+      </c>
+      <c r="C52" s="26">
+        <v>45939</v>
+      </c>
+      <c r="D52" s="23">
+        <v>134724143</v>
+      </c>
+      <c r="E52" s="18">
+        <v>3450096331</v>
+      </c>
+      <c r="F52" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="G52" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H52" s="66" t="s">
+        <v>131</v>
+      </c>
+      <c r="I52" s="50">
+        <v>45931</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
+      <c r="A53" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B53" s="7">
+        <v>45930</v>
+      </c>
+      <c r="C53" s="26">
+        <v>45939</v>
+      </c>
+      <c r="D53" s="23">
+        <v>134727296</v>
+      </c>
+      <c r="E53" s="18">
+        <v>3450095792</v>
+      </c>
+      <c r="F53" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="G53" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H53" s="66" t="s">
+        <v>131</v>
+      </c>
+      <c r="I53" s="50">
+        <v>45930</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
+      <c r="A54" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B54" s="70">
+        <v>45930</v>
+      </c>
+      <c r="C54" s="67">
+        <v>45939</v>
+      </c>
+      <c r="D54" s="23">
+        <v>134727457</v>
+      </c>
+      <c r="E54" s="18">
+        <v>3450095539</v>
+      </c>
+      <c r="F54" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="G54" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H54" s="66" t="s">
+        <v>131</v>
+      </c>
+      <c r="I54" s="50">
+        <v>45930</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
+      <c r="A55" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B55" s="70">
+        <v>45930</v>
+      </c>
+      <c r="C55" s="50">
+        <v>45939</v>
+      </c>
+      <c r="D55" s="68">
+        <v>134727484</v>
+      </c>
+      <c r="E55" s="18">
+        <v>3450095517</v>
+      </c>
+      <c r="F55" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="G55" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H55" s="66" t="s">
+        <v>131</v>
+      </c>
+      <c r="I55" s="50">
+        <v>45930</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
+      <c r="A56" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B56" s="70">
+        <v>45930</v>
+      </c>
+      <c r="C56" s="50">
+        <v>45939</v>
+      </c>
+      <c r="D56" s="68">
+        <v>134727605</v>
+      </c>
+      <c r="E56" s="18">
+        <v>3450095352</v>
+      </c>
+      <c r="F56" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="G56" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H56" s="66" t="s">
+        <v>131</v>
+      </c>
+      <c r="I56" s="50">
+        <v>45930</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
+      <c r="A57" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B57" s="70">
+        <v>45930</v>
+      </c>
+      <c r="C57" s="50">
+        <v>45939</v>
+      </c>
+      <c r="D57" s="68">
+        <v>134727680</v>
+      </c>
+      <c r="E57" s="18">
+        <v>3450095308</v>
+      </c>
+      <c r="F57" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="G57" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H57" s="66" t="s">
+        <v>131</v>
+      </c>
+      <c r="I57" s="50">
+        <v>45930</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
+      <c r="A58" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B58" s="70">
+        <v>45930</v>
+      </c>
+      <c r="C58" s="50">
+        <v>45939</v>
+      </c>
+      <c r="D58" s="68">
+        <v>134728030</v>
+      </c>
+      <c r="E58" s="18">
+        <v>3450094659</v>
+      </c>
+      <c r="F58" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="G58" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H58" s="66" t="s">
+        <v>131</v>
+      </c>
+      <c r="I58" s="50">
+        <v>45930</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
+      <c r="A59" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="B59" s="50">
+        <v>45931</v>
+      </c>
+      <c r="C59" s="63">
+        <v>45939</v>
+      </c>
+      <c r="D59" s="68">
+        <v>134732752</v>
+      </c>
+      <c r="E59" s="18">
+        <v>3450096903</v>
+      </c>
+      <c r="F59" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="G59" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H59" s="66" t="s">
+        <v>131</v>
+      </c>
+      <c r="I59" s="50">
+        <v>45931</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="2">
+    <cfRule type="notContainsBlanks" priority="3">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A18" xr:uid="{69840FBE-03D6-48CB-B553-2E7186E1B4BD}">
-      <formula1>$J$2</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A59" xr:uid="{69840FBE-03D6-48CB-B553-2E7186E1B4BD}">
+      <formula1>#REF!</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G41" xr:uid="{AF5C7196-9DAE-4339-82D4-9412023E2B2A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G59" xr:uid="{AF5C7196-9DAE-4339-82D4-9412023E2B2A}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7089,57 +8399,55 @@
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-496593</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-496593</Url>
-      <Description>QAFFA7D2F2TC-2102087286-496593</Description>
-    </_dlc_DocIdUrl>
-    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </DossierOwner>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ccca9d190a3c43e89f73773ee806c8b5>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ia4b831ccad64069ad2e0cbd870e9b8a>
-    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </alteradopor>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="44" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ac14f8cb44178d381f4c0afb30680a90">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5e58414b065c9b590c40efa77cd84bb6" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -7517,68 +8825,70 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-496593</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-496593</Url>
+      <Description>QAFFA7D2F2TC-2102087286-496593</Description>
+    </_dlc_DocIdUrl>
+    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </DossierOwner>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ccca9d190a3c43e89f73773ee806c8b5>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ia4b831ccad64069ad2e0cbd870e9b8a>
+    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </alteradopor>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32450128-80FB-4462-BDF1-414021F91FB7}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32450128-80FB-4462-BDF1-414021F91FB7}"/>
-</file>
-
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
 </file>